--- a/baza-rossiya.xlsx
+++ b/baza-rossiya.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="база 50" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="резерв" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="есть сайт (убраны)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -440,6 +441,7 @@
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="80" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -521,6 +523,11 @@
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>часы работы</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>проверка сайта</t>
         </is>
       </c>
     </row>
@@ -604,6 +611,11 @@
           <t>ежедневно 10:00-20:00</t>
         </is>
       </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>сайт был (точкамебели.рф), сейчас домен не работает</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -613,231 +625,61 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Владивосток</t>
+          <t>Оренбург</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Сити мебель, мебельная фабрика</t>
+          <t>Мебель Концепт 56, мебельная компания</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Перегородки, Изделия из камня для помещений</t>
+          <t>Мебель на заказ, Мебель для кухни, Офисная мебель, Корпусная мебель</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>298</v>
+        <v>138</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>taplink (http://taplink.cc/concept056)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79020504333</t>
+          <t>https://t.me/+79033662614</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79241237111</t>
+          <t>https://wa.me/79033662614</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>+7‒924‒123‒71‒11</t>
+          <t>+7‒903‒366‒26‒14</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Выселковая улица, 39</t>
+          <t>проезд Автоматики, 12 лит В</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/vladivostok/firm/70000001027532472</t>
+          <t>https://2gis.ru/orenburg/firm/70000001088992897</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>https://i2.photo.2gis.com/images/branch/0/30258560057154802_2f85.jpg
-https://i6.photo.2gis.com/images/branch/0/30258560057154801_e62c.jpg
-https://i8.photo.2gis.com/images/branch/25/3518437227585068_e41f.jpg
-https://i0.photo.2gis.com/images/branch/0/30258560057154800_fbda.jpg
-https://i2.photo.2gis.com/photo-gallery/e6e137ad-6992-408e-bdde-dc607c63c3cb.jpg
-https://i8.photo.2gis.com/photo-gallery/e1364147-12f9-4254-a0d2-5d4f47b27b81.jpg</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>«Искали узкий шкаф-купе в коридор, чтобы не перекрывал проход. В Сити Мебель нашли подходящий вариант. Двери выбрали зеркальные во весь рост, коридор теперь визуально кажется шире и светлее. Профиль ходит бесшумно, шкаф то что надо!» (Дина ., 2026-10-12)
-«Ставлю пятерку нашей прихожей. Красиво получилось, очень гармонично сочетается с нашим кухонным гарнитуром, смотрится как с одного набора. Уже порекомендовал вас сестре как хорошую мебельную компанию😏» (Матвей vl, 2026-10-09)
-«Шкаф отличный! Цвет подошел под кровать один в один. Вместительный, полок внутри сделали много, как я и просила. Никаких сколов или царапин при доставке не обнаружила» (Кира Демина, 2026-10-05)</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>ежедневно 09:30-18:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Тюмень</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Аватти, студия мебели</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Детская мебель, Мебель для ванных комнат, Изделия из камня для помещений, Офисная мебель</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>231</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/+79582526486</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>https://wa.me/79582526486</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>+7‒958‒252‒64‒86</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>улица Пожарных и спасателей, 3 к1</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>https://2gis.ru/tyumen/firm/70000001064905837</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>https://i8.photo.2gis.com/photo-gallery/ee9e285a-78d2-4397-b9d7-50d5945e1c31.jpg
-https://i8.photo.2gis.com/photo-gallery/4d6ef170-63a6-474e-ac43-d36124ee019c.jpg
-https://i1.photo.2gis.com/photo-gallery/54de5545-a2a7-441b-9b0b-3ba72ed3b867.jpg
-https://i1.photo.2gis.com/photo-gallery/40e93371-f0a9-4d96-93b7-1570ff215d16.jpg
-https://i5.photo.2gis.com/photo-gallery/f112d56d-59e0-4254-928b-7d3749fc6827.jpg
-https://i8.photo.2gis.com/photo-gallery/9f8f402d-8a18-4ae7-aded-712629071c05.jpg</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>«Заказывал встроенный шкаф в спальню. Замерщик все замерил, менеджер в салоне все нарисовала, посоветовала цвета и материалы. Встало идеально, двери ходят плавно и без звука) Фурнитура надежная.» (Ростислав Титов, 2026-10-12)
-«Делали встроенный шкаф в нишу. Зазоры идеальные, как будто там и был. Фурнитура надежная, двери закрываются очень плавно.» (Юра Твердохлебов, 2026-10-07)
-«Заказывали комод и тумбу под ТВ в гостиную. Дизайн выбрали сами, в Аватти воплотили в жизнь. Смотрится стильно, ящики выдвигаются плавно.» (Алина Копылова, 2026-10-04)</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>пн выходной, вт-пт 11:00-20:00, сб 11:00-18:00, вс выходной</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Оренбург</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Мебель Концепт 56, мебельная компания</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Мебель на заказ, Мебель для кухни, Офисная мебель, Корпусная мебель</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>taplink (http://taplink.cc/concept056)</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/+79033662614</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>https://wa.me/79033662614</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>+7‒903‒366‒26‒14</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>проезд Автоматики, 12 лит В</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>https://2gis.ru/orenburg/firm/70000001088992897</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>https://i9.photo.2gis.com/photo-gallery/cc4a8ca6-7267-43fc-afc4-21a6cffce369.jpg
 https://i6.photo.2gis.com/photo-gallery/d2d892f8-d037-4762-95bf-a35fadcd2301.jpg
@@ -847,78 +689,83 @@
 https://i7.photo.2gis.com/photo-gallery/16d2acff-67fa-4a61-a7cd-43a180a88590.jpg</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>«Мебель Концепт 56 приятно удивил уровнем сервиса. Менеджеры помогли с выбором, а готовая мебель оказалась просто отличной.» (ALEKSANDR ALESHIN, 2026-10-14)
 «Очень довольны сотрудничеством с компанией Мебель Концепт 56. Мебель качественная, стильная и полностью соответствует нашим ожиданиям.» (Татьяна Абрамова, 2026-10-09)
 «заказали тут кухню по совету друзей. Нам понравилось с вами сотрудничать изготовили в срок установили быстро. От кухни восторге» (Гриша Каримов, 2026-10-05)</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>ежедневно 10:00-19:00</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Челябинск</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Диамант, мебельный салон</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E4" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>4.9</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>https://t.me/+79507404273</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>+7‒950‒740‒42‒73</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Каслинская улица, 23</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/chelyabinsk/firm/70000001081038759</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>https://i6.photo.2gis.com/photo-gallery/72c1d0ed-afcf-42ce-b380-b8c7226efb90.jpg
 https://i3.photo.2gis.com/photo-gallery/d4fd00ab-7e27-453d-b01b-203d361ba5df.jpg
@@ -928,332 +775,87 @@
 https://i8.photo.2gis.com/photo-gallery/1ac3778d-0643-4ee2-93ed-ea36842847fc.jpg</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>«Давно мечтала о кухне с островом, и Диамант воплотил мечту в реальность! Места теперь хватает всей нашей большой семье. Готовить одно удовольствие.» (Любовь Беликова, 2026-10-17)
 «Сборка прошла на удивление быстро и чисто. Мастера даже пропылесосили за собой. Приятно удивлен таким сервисом.» (Тимур Ласточкин, 2026-10-16)
 «Ксения - волшебница! Помогла выбрать такой сложный оттенок для фасадов, который идеально вписался в интерьер. Я в восторге))» (Анна Демидова, 2026-10-15)</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>ежедневно 10:00-21:00</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Тюмень</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Шкаф, офис продаж</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Мебель на заказ, Мягкая мебель, Детская мебель, Мебель для кухни, Корпусная мебель, Офисная мебель, Мебельные фасады, Изделия из камня для помещений, Мебель для ванных комнат, Мебель для культурно-досуговых учреждений, Мебель для общественного питания, Медицинская и лабораторная мебель, Мебель для учебных учреждений, Металлическая мебель, Мебель из стекла, Мебель для салонов красоты, Распиловка древесины, ЛДСП, ДВПО, МДФ</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Красноярск</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Мастерская дизайна</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/+79088742331</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>+7‒904‒498‒49‒44</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>Полевая улица, 109 ст1</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>https://2gis.ru/tyumen/firm/70000001055443836</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>https://i9.photo.2gis.com/photo-gallery/76761e78-fb99-4122-803e-83fd47cc1cb4.jpg
-https://i3.photo.2gis.com/photo-gallery/1643ccf1-f561-4224-8bb7-ecb6ffde07bd.jpg
-https://i8.photo.2gis.com/photo-gallery/3b6f5a3a-3264-484f-a259-50266b3ff040.jpg
-https://i2.photo.2gis.com/photo-gallery/1a00f868-21ab-4357-ba4d-baa103eef6d9.jpg
-https://i9.photo.2gis.com/images/branch/0/30258560065180483_0b16.jpg
-https://i0.photo.2gis.com/photo-gallery/9731fdc4-ea41-43e8-bd0c-37a2030da8d1.jpg</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>«Заказывали изголовье для кровати, сделали все качественно. На всех этапах специалисты (замерщик, менеджер, сборщик) квалифицированные. Однозначно рекомендуем!» (Karen P., 2026-06-08)
-«Заказывали шкаф и комод для обуви в прихожую. Индивидуальный подход и качественная работа.» (Екатерина Терехова, 2026-04-07)
-«Заказали кухню! Все сделано в срок! Спасибо большое менеджеру Анастасии! Вытерпела меня ))). При доставке уронили шкаф, повредили ножку, тут же при нас позвонили монтажникам, они привезли новую . Кухней полностью довольна! Спасибо! 🙏» (мария Р, 2025-11-16)</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>пн-пт 09:00-18:00, сб 10:00-16:00, вс выходной</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Ависта, мебельная компания</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Мебель на заказ, Мебельные фасады, Мебель для кухни, Корпусная мебель</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>https://wa.me/79132102115</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>+7 (3852) 299‒922</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>проспект Космонавтов, 34ж</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>https://2gis.ru/barnaul/firm/563478234632390</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>https://i4.photo.2gis.com/photo-gallery/0ba32cbc-3259-457b-abe2-6d81f86229c5.jpg
-https://i3.photo.2gis.com/photo-gallery/ff3ec41a-523d-4301-8059-641d443175aa.jpg
-https://i6.photo.2gis.com/photo-gallery/cb7bdd4f-d5d0-4e1e-98bc-d2f7667576f5.jpg
-https://i3.photo.2gis.com/photo-gallery/9c4cae10-4488-4754-a4d9-56c4946e4886.jpg
-https://i7.photo.2gis.com/photo-gallery/1c0568da-4c1e-4086-b083-971ce0c45c9c.jpg
-https://i1.photo.2gis.com/photo-gallery/dfd04959-16d0-4e3e-9de1-d8bf907ae12c.jpg</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>«Очень хорошая мебельная компания! Рекомендую!!!» (Vlada, 2026-04-10)
-«Отличная организация по изготовлению мебельных фасадов .
-Менеджеры помогут и расскажут какие материалы лучше и на какую мебель подойдут /либо это кухня. Спальня .
-или ванная комната 
-Добавляют новые материалы» (Виталий Грибанов, 2026-02-06)
-«Делал шкафчик в санузел, тумбу под раковину и обрамление зеркала в едином стиле. Молодцы, сделали все аккуратно. Три года прошло эксплуатации. Все работает, вид как у нового изделия.» (Роман Гридневский, 2025-09-08)</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>пн-пт 09:00-18:00, сб 09:00-14:00, вс выходной</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Саратов</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1001Идея, мебельная компания</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Детская мебель, Офисная мебель</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>taplink (http://taplink.cc/1001idea)</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/+79020428371</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>https://wa.me/79020428371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>+7 (8452) 60‒15‒15</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>Геофизическая улица, 9</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>https://2gis.ru/saratov/firm/70000001054576304</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>https://i4.photo.2gis.com/photo-gallery/88529c9c-c146-455d-80d4-82f44deed398.jpg
-https://i9.photo.2gis.com/photo-gallery/42e66c73-6f4a-462b-9922-ece8f949c27d.jpg
-https://i9.photo.2gis.com/photo-gallery/b8f028fe-21c6-41a7-b6d8-ac560f5cacdc.jpg
-https://i7.photo.2gis.com/photo-gallery/e4c81d16-2ef0-4cd6-ab80-3d1026ddecd1.jpg
-https://i0.photo.2gis.com/photo-gallery/e20c2dff-6795-401c-beb3-444f4315270f.jpg
-https://i9.photo.2gis.com/images/branch/0/30258560098242010_bbce.jpg</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>«Мебель супер! Выглядит дорого, собрана идеально, пользоваться удобно. Никаких проблем ни при сборке, ни в эксплуатации. Рекомендую на 100 %» (Татьяна Марченкова, 2026-08-07)
-«Заказываю мебель только здесь! Коллектив - каждый из них профессионал! Любую мечту воплотят в реальность!» (Ольга Еременкова, 2026-05-16)
-«Не так давно обращалась за услугами в эту компанию. Всё прошло согласно договору. Выполнения работ были в срок. Качество мебели хорошее. Проект и сборка были выполнены профессионально. Общее впечатление отличное.» (Альфия Адаева, 2026-05-16)</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>пн-пт 09:00-18:00, сб 10:00-15:00, вс выходной</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Красноярск</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Мастерская дизайна</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>https://t.me/+79131773957</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/79131773957</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>+7‒913‒177‒39‒57</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>улица Шахтёров, 65</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/krasnoyarsk/firm/70000001019390807</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>https://i8.photo.2gis.com/photo-gallery/8489f0e3-2f87-4a18-8d24-fb51a405fcec.jpg
 https://i8.photo.2gis.com/photo-gallery/9fccd053-349e-444c-9338-ac4e5de79bae.jpg
@@ -1263,155 +865,83 @@
 https://i7.photo.2gis.com/photo-gallery/b11581d7-1f2e-44b3-b46b-1745d5624736.jpg</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>«Идеальный сервис от и до! Заказывали мебель и технику с установкой под ключ. Работа руководства и мастеров максимально слаженная, подход к клиенту отличный. Качеством сборки и отношением очень довольны. Рекомендую на все 100%» (Дмитрий P, 2026-07-08)
 «Делали у ребят кухню, книжный шкаф и тумбу под телевизор! Очень понравилось работать, все досконально замеряют, учитывают каждый нюанс, если вам важны детали, то точно обращайтесь к ним!» (Юлия Разумкина, 2026-05-06)
 «Обращаемся в мастерскую дизайна уже не в первый раз, качество на высоте. Все сотрудники мастера своего дела, ответственные, Екатерина воплощает все наши пожелания!!! Мы довольны вашей работой.» (Вера Монич, 2026-01-08)</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>ежедневно 10:00-19:00</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>GaStone, фабрика мебели</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель, Мебель для ванных комнат, Облицовочный камень</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/+79225601631</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>Цвиллинга, 1</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>https://2gis.ru/ekaterinburg/firm/70000001100412421</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>https://i3.photo.2gis.com/photo-gallery/c1f72ce4-343e-4337-b0bb-d29954ed176a.jpg
-https://i0.photo.2gis.com/photo-gallery/a0ad0541-7113-4506-ada5-22f67d84b020.jpg
-https://i8.photo.2gis.com/photo-gallery/9895bad0-cbe3-4024-99b9-c18281b771eb.jpg
-https://i2.photo.2gis.com/photo-gallery/e8b4a090-20b1-48af-b89a-809f8cc53289.jpg
-https://i5.photo.2gis.com/photo-gallery/e57aa358-92d4-4694-ab24-ac6399fc1416.jpg
-https://i1.photo.2gis.com/photo-gallery/529695b4-c79b-45ac-9134-5d14e12c8493.jpg</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>«Хороший салон, внимательные менеджеры. Заказывали кухню клиентам (Я дизайнер интерьера), все получилось, как задумывались в проекте. Возникали конечно и спорные моменты, но их решали в процессе оперативно. Советую. Работали с Оксаной, приятно было общаться.» (Анастасия Цветкова, 2026-09-20)
-«Отличная компания, сделали все качественно, отдельное спасибо менеджеру Екатерине, рекомендую при выборе и заказе кухни.» (Ilya Kochegarov, 2025-11-06)
-«Добрый день. Заказывали 2 года назад кухонный гарнитур. Екатерина Соловьева сразу поняла  что нам надо, хотя мы сами с трудом понимали . Все рекомендации Екатерины и по сей день радуют. Кухню установили качественно в срок.» (Tatyana Gorbunova, 2025-10-28)</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>ежедневно 10:00-19:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Тюмень</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Mebelm, студия мебели</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Мебель на заказ, Мебельные магазины, Корпусная мебель, Мебель для кухни, Детская мебель, Офисная мебель</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E6" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>соцсети (http://t.me/mebm72)</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>https://t.me/mebelm72</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>+7‒929‒269‒52‒94</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>улица Федюнинского, 43</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/tyumen/firm/70000001069445291</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>https://i0.photo.2gis.com/photo-gallery/a82d491a-04c4-4a94-a3bb-643de74fa396.jpg
 https://i8.photo.2gis.com/photo-gallery/37ab22c0-c946-4e68-9ce4-f2aa7daea0e8.jpg
@@ -1421,161 +951,83 @@
 https://i6.photo.2gis.com/photo-gallery/74dae07b-363a-4757-a502-1271e0de80ce.jpg</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>«Хочу выразить благодарность менеджеру Ладе, за отличную работу на этапе заказа. Мы только что оформили договор на покупку кухни, саму мебель еще ждем. Лада, учла все наши пожелания и предложила удобные варианты планировки.» (Оксана Самарцева, 2026-09-10)
 «Заказали в МебельМ кухню, удалось вписаться в бюджет! Ждём изготовления и установки.» (Игорь М, 2026-08-18)
 «Все было отлично очень советую менеджер Александра спасибо вам отлично проконсультировали мастер своего дела спасибо !» (Владимир Астахов, 2026-08-07)</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>ежедневно 10:00-21:00</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Тюмень</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Paderin, мебельная мастерская</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель, Офисная мебель, Детская мебель, Мебель для ванных комнат</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Иркутск</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Сандера, студия кухни и корпусной мебели</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/+79923112860</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>+7 (3452) 70‒21‒02</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>улица Фармана Салманова, 18</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>https://2gis.ru/tyumen/firm/70000001087652176</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>https://i1.photo.2gis.com/photo-gallery/71298f27-135b-4bd6-ac7c-70d5c6f19f44.jpg
-https://i5.photo.2gis.com/photo-gallery/7e5992e6-b6af-4ce1-a66b-c66c05d2ffb8.jpg
-https://i1.photo.2gis.com/photo-gallery/4875e65d-f0a2-43ff-bd99-f3c4efb35b58.jpg
-https://i3.photo.2gis.com/photo-gallery/6d6f242e-f113-472b-a5fb-cf55ab50b94a.jpg
-https://i7.photo.2gis.com/photo-gallery/7ba7e8be-b6c9-429e-9db0-445ecbf40081.jpg
-https://i5.photo.2gis.com/photo-gallery/bed6bb00-e282-4300-9b15-4b9c438ca757.jpg</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>«Замечательное место, атмосферное ❤️ быстро все изготавливают и качественно. Особенно хочется отметить фею мебели Жанну Дамзову✨🫶» (Полина Хабибуллина, 2025-03-21)
-«Спасибо большое команде Paderin!!
-От разработки проекта,до установки кухни,все было на высшем уровне.
-Желаю вам процветания и побольше благодарных клиентов!🌸» (Анастасия Гуцуляк, 2026-07-14)
-«Делали нам кухню,все замечательно,посоветовали,что нам нужно и материал и технику! Менеджер Жанна, была всегда на связи по любым вопросам! Советую ! Оплата с рассрочкой,это очень удобно!» (Зоя Степанова, 2026-05-22)</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>пн-пт 10:00-19:00, сб-вс 10:00-18:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Иркутск</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Сандера, студия кухни и корпусной мебели</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>https://t.me/+79247057628</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>+7‒924‒600‒33‒03</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>улица Рабочего Штаба, 66</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/irkutsk/firm/70000001065493213</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>https://i2.photo.2gis.com/images/branch/0/30258560173175962_889c.jpg
 https://i1.photo.2gis.com/photo-gallery/15bfbad6-9208-4708-9a62-2e53b06c5bc1.jpg
@@ -1585,7 +1037,7 @@
 https://i0.photo.2gis.com/photo-gallery/4ca68973-6bce-4939-bca2-ff8a48793416.jpg</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>«Заказывали шкаф именно в данной компании по рекомендации коллег.
 Отличный сервис,все изготовили и установили точно в срок.Хорошо,что компания предоставляет от себя рассрочку,это удобно.
@@ -1595,71 +1047,76 @@
 Про гарнитур подруги сказали, что это мечта любой хозяйки))» (Мария Стрыгина, 2026-05-20)</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>пн выходной, вт-сб 11:00-19:00, вс выходной</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Красноярск</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Мебелиссимо</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Мебель на заказ, Корпусная мебель, Детская мебель, Мебель для ванных комнат, Мебель для кухни</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E8" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/79130397007</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>+7‒913‒039‒70‒07</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>улица Академика Вавилова, 1 ст9</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/krasnoyarsk/firm/70000001056207594</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>https://i1.photo.2gis.com/photo-gallery/a5971d5d-bc29-4e3f-b1a0-1229eda79bd8.jpg
 https://i4.photo.2gis.com/images/branch/0/30258560065176713_1714.jpg
@@ -1669,7 +1126,7 @@
 https://i2.photo.2gis.com/photo-gallery/1f65b1b9-172b-4334-abac-a3eb49357a3a.jpg</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>«Делала ремонт родителям, заказывала всю мебель тут. Оптимальное соотношение цена/качество. Ответственная компания, сроки выдержаны, хорошие монтажники, все мелкие нюансы доведены до конечного результата 👌
 Советую!» (Анна Данильченко, 2026-05-28)
@@ -1677,71 +1134,76 @@
 «Сделали раньше срока, на всех этапах помогали и консультировали, подсказывали, изготовили и установили идеально, все зазоры ровные ( в плоть) до миллиметра, огромное спасибо Денису и мастеру Александру за шикарную кухню!» (Семён Клявзер, 2026-03-23)</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>пн-пт 10:00-19:00, сб 10:00-15:00, вс выходной</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>под вопросом: ник ВК совпадает с kukhni-krasnoyarsk.ru, но телефон на сайте другой, похоже на чужой сайт-агрегатор</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Иркутск</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Кухни-Тейге, компания по производству кухонь и шкафов</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Мебель на заказ, Офисная мебель, Мебель для ванных комнат, Детская мебель, Корпусная мебель, Мебель для кухни</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>4.7</v>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>https://t.me/+79148810902</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>+7‒908‒774‒46‒22</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Байкальская улица, 126/3</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/irkutsk/firm/70000001056539637</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>https://i8.photo.2gis.com/photo-gallery/9448c8f9-1d09-4a01-86fd-194d330887a0.jpg
 https://i1.photo.2gis.com/photo-gallery/79bb0b2f-c1c9-47f6-8d68-14af37af7bb1.jpg
@@ -1751,16 +1213,650 @@
 https://i2.photo.2gis.com/photo-gallery/3232cd3f-be5d-4128-97b8-a86c46449eca.jpg</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>«Заказывали год назад кухню. Илья сразу предупредил, что ожидание примерно 3-4 месяца. Но это того стоило. Теперь это наше любимое место в доме. Кухня просторная и многофункциональная. Спасибо большое.» (Евгения Дейнеко, 2026-09-10)
 «Не место красит человека а человек место, предельно честный диалог, а это в наше время далеко не последнее качество. Соотношение цены и качество - безупречно. Рекомендую !!!» (Светлана Шурыгина, 2026-06-02)
 «Подход к тем, которые только планируют кухонный гарнитур. Предлагая варианты и нужные решения» (Александр Сорокин, 2025-07-19)</t>
         </is>
       </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>ежедневно 09:00-21:00</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Воронеж</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Reroom</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Мебель на заказ, Мебель для кухни, Мебель для ванных комнат, Корпусная мебель, Изделия из камня для помещений</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/+79202222306</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/79202222306</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>+7‒920‒222‒23‒06</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>улица Лётчика Колесниченко, 65а</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>https://2gis.ru/voronezh/firm/70000001067470840</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>https://i7.photo.2gis.com/images/branch/0/30258560168471449_6e6a.jpg
+https://i6.photo.2gis.com/images/branch/0/30258560168471439_5047.jpg
+https://i2.photo.2gis.com/images/branch/0/30258560168471441_0ab4.jpg
+https://i4.photo.2gis.com/images/branch/0/30258560168471446_8239.jpg
+https://i5.photo.2gis.com/images/branch/0/30258560168471452_e5b6.jpg
+https://i3.photo.2gis.com/images/branch/0/30258560168471444_12e1.jpg</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>«Работой компании Reroom осталась довольна, кухонный гарнитур изготовили по необходимым размерам, доставили и установили качественно и в срок. Учли все пожелания!» (Евгения Тарасова, 2026-10-13)
+«Отличное соотношение цены и качества, доступные цены, кухня выглядит стильно и современно.» (Альбина Воронина, 2026-10-06)
+«Давно выбирала кухню. Пересмотрела кучу вариантов и выбор остановился на компании Reroom.Всё делают быстро, качественно, всем довольна» (Ксю Ник, 2026-10-04)</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>ежедневно 10:00-19:00</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Тюмень</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Студия мебели 72</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Детская мебель</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/+79220751863</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>+7 (3452) 933‒424</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Николая Чаплина улица, 115</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>https://2gis.ru/tyumen/firm/70000001033925374</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>https://i3.photo.2gis.com/images/branch/0/30258560082794661_483f.jpg
+https://i4.photo.2gis.com/images/branch/13/1829587396678755_f370.jpg
+https://i7.photo.2gis.com/images/branch/13/1829587396678783_09e6.jpg
+https://i9.photo.2gis.com/photo-gallery/f83c949c-7c6e-40b6-be3f-be74cc2aad99.jpg
+https://i1.photo.2gis.com/images/branch/13/1829587396678601_9a38.jpg
+https://i8.photo.2gis.com/photo-gallery/f2268bf2-5e39-40e2-990b-5db65d4d5a99.jpg</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>«Лучшая студия для заказа мебели . Уже 4 года на постоянной основе желаем заказ.
+Менеджер Екатерина, мастеры Константин и Вадим все профессионалы с большой буквы . Качество и сервис на высоте ! Спасибо ❤️» (Тали Долгополова, 2026-07-24)
+«Заказала кухню и осталась довольна! Ребята сборщики молодцы, старались и всё качественно!Спасибо большое!» (Ольга Федорова, 2025-03-03)
+«Заказывала мебель, очень довольна 
+И за качество мебели и за выполнению работу. Выполнили все своевременно. Обращаюсь не в первый раз» (Гавва Хусейнова, 2025-03-01)</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>пн-пт 10:00-18:00, сб-вс 11:00-17:00</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Престиж, мебельный салон</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Мебель на заказ, Мебельные магазины, Мягкая мебель, Корпусная мебель</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/prestizh22</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/79646037139</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>+7‒964‒603‒71‒39</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Павловский тракт, 251ж</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>https://2gis.ru/barnaul/firm/70000001025293075</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>https://i1.photo.2gis.com/photo-gallery/f67ec993-3083-44a5-9811-0f45cbc8468f.jpg
+https://i1.photo.2gis.com/images/branch/0/30258560085749641_2bb2.jpg
+https://i4.photo.2gis.com/images/branch/0/30258560083552260_8949.jpg
+https://i3.photo.2gis.com/images/branch/0/30258560080947293_17f6.jpg
+https://i7.photo.2gis.com/photo-gallery/f16bc816-47f7-45d1-a769-130a611ef846.jpg
+https://i2.photo.2gis.com/images/branch/0/30258560081105444_7f4a.jpg</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>«Приобрёл кровать, матрац и диван, работа консультанта отличная, цены адекватные, модели изделий в красивом дизайне, ни как у большинства фабрик! Жду поставку мебели, надеюсь придет в отличном качестве!» (Алим Абдуллаев, 2026-07-24)
+«Купил шкаф-купе, очень доволен качеством. Отдельная благодарность мастерам Алексею и Сергею, которые учли все пожелания и собрали шкаф очень хорошо и качественно.» (Никита Колодченко, 2025-07-17)
+«Сегодня нам привезли и поставили прихожую,все оперативно быстро, мусор за собой убрали,все аккуратно, спасибо парням. Срок изготовления 20 дней.» (Светлана Нечаева, 2025-05-13)</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>ежедневно 10:00-21:00</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Томск</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Marle, студия мебели</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>соцсети (http://t.me/marletmsk)</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/+79131111387</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/79234577445</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>+7‒9‒234‒577‒445</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>улица Пушкина, 59/1</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>https://2gis.ru/tomsk/firm/70000001063814452</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>https://i1.photo.2gis.com/photo-gallery/88bf2580-4089-49ff-a170-39d7993e5d93.jpg
+https://i4.photo.2gis.com/photo-gallery/14a4d18a-b053-443e-a3bd-92857a358250.jpg
+https://i3.photo.2gis.com/photo-gallery/25536f52-e8be-4ad6-9e82-979a17b648a0.jpg
+https://i4.photo.2gis.com/photo-gallery/cd2521c7-f3c0-4e52-a185-f1d6472fd438.jpg
+https://i1.photo.2gis.com/photo-gallery/91ead9c0-f4ba-45d2-83b4-c45e02911feb.jpg
+https://i5.photo.2gis.com/photo-gallery/0bbeb0c7-c848-4819-9ae0-20ed6059306a.jpg</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>«Узнали о компании по рекомендации. Обращалась по изготовлению детской в дом . Сразу поняли друг друга и подобрали идеальный цвет и размер. Вежливый персонал. Также порадовала бесплатная доставка и установка. Однозначно рекомендую» (Рамазан, 2026-10-02)
+«С этой компанией уже больше 5 лет. Ставили себе и старшей дочери. Сейчас установили кухню и шкаф в новую квартиру. Все как всегда шикарно, а главное со вкусом» (Татьяна Краюхина, 2026-09-28)
+«В этой компании делали заказ новой кухни маме в подарок на юбилей. Привезли и собрали мебель в срок. Качество достойное, внешне кухня смотрится отлично» (Дарья Коровина, 2026-09-24)</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>ежедневно 10:00-21:00</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Владивосток</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>ИнДом, торгово-производственная компания</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Офисная мебель, Распиловка древесины, Мебель для ванных комнат, Детская мебель</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>taplink (http://taplink.cc/indom)</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/+aZJHfuP5ChQzNTRi</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/79089939190</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>+7‒908‒993‒91‒90</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Можайская улица, 28в</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>https://2gis.ru/vladivostok/firm/3518965489996252</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>https://i4.photo.2gis.com/images/branch/0/30258560079429485_dbcb.jpg
+https://i1.photo.2gis.com/images/branch/0/30258560077847459_d1f6.jpg
+https://i5.photo.2gis.com/images/branch/0/30258560077958910_8cd3.jpg
+https://i4.photo.2gis.com/images/branch/0/30258560090578744_15a4.jpg
+https://i0.photo.2gis.com/images/branch/0/30258560090578812_c82d.jpg
+https://i3.photo.2gis.com/images/branch/0/30258560093474605_3a46.jpg</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>«Все понравилось. Сделали в срок. Полная консультация по всем материалам.
+Спасибо.» (Денис Мельников, 2026-10-01)
+«Отличная работа, ребята сделали качественно, спасибо большое 😘😘😘» (Prince.Almaty Alex, 2026-02-17)
+«Спасибо ребятам, все сделал очень хорошо. Цена вполне удовлетворительная, а качество на высоте! Возможно ещё закажем какую-то мебель» (Городской житель, 2025-12-19)</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>ежедневно 10:00-17:00</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Текстура, семейная студия мебели и интерьерных решений</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Мебель на заказ, Корпусная мебель, Дизайн интерьеров, Офисная мебель, Мебель для кухни, Детская мебель, Мебель для ванных комнат, Торгово-выставочное оборудование</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/+79923303208</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/79292120201</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>+7‒992‒330‒32‒08</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Мраморская улица, 6</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>https://2gis.ru/ekaterinburg/firm/70000001064278509</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>https://i2.photo.2gis.com/images/branch/0/30258560131054986_d293.jpg
+https://i3.photo.2gis.com/images/branch/0/30258560131013185_0e7a.jpg
+https://i2.photo.2gis.com/images/branch/0/30258560131248747_519a.jpg
+https://i6.photo.2gis.com/images/branch/0/30258560131464333_368b.jpg
+https://i5.photo.2gis.com/images/branch/0/30258560131037080_8292.jpg
+https://i3.photo.2gis.com/images/branch/0/30258560131054984_8e68.jpg</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>«Уже почти год любуюсь самой красивой кухней💜
+Спасибо Станиславу за то, что каждый шкафчик в квартире собирал с душой.
+Отдельно отмечу, что небольшие нюансы корректируются оперативно и без проблем.» (Татьяна Идамжапова, 2026-05-18)
+«В декабре заказывали здесь кухню))
+Изготовили быстро, также быстро и установили. Очень рада, что свою кухню доверила профессионалам🥰 создали шикарный проект.» (Даша Егорова, 2026-02-04)
+«Не первый раз заказываем мебель у Ксении и Станислава. Два года назад установили отличную кухню. Теперь дошла очередь до шкафа в спальню. Результатом довольны! Отдельно замечу - не смотря на проблемы со стенами, Стас установил все идеально, до миллиметра 👍👍👍» (Alexander Pribylov, 2025-04-27)</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>ежедневно 11:00-20:00</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Махачкала</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Нова, салон мебели</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Мебель на заказ, Мебельные магазины, Корпусная мебель, Детская мебель, Мягкая мебель</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>соцсети (http://t.me/novamebel05)</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/79884403011</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>+7‒988‒440‒30‒11</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>проспект Гамидова, 81/2</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>https://2gis.ru/makhachkala/firm/70000001021645284</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>https://i7.photo.2gis.com/photo-gallery/9321abb7-29e9-48a5-8668-7c10200875b9.jpg
+https://i4.photo.2gis.com/photo-gallery/cbf6e432-9022-4dcc-ad34-55f0214f77ae.jpg
+https://i7.photo.2gis.com/photo-gallery/c2102357-6933-4f6a-9b9f-e12cdbefee7f.jpg
+https://i0.photo.2gis.com/photo-gallery/35361992-e47c-4971-a03f-0f469bfa6eae.jpg
+https://i0.photo.2gis.com/photo-gallery/20cbc26d-efeb-46c3-a567-c7a6f8c94eca.jpg
+https://i1.photo.2gis.com/photo-gallery/0ef2eb4d-89ae-4ca5-acfa-a7bdd91c1454.jpg</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>«Все шикарно! Очень довольна ! Советую!!!» (Саида Цахаева, 2026-09-12)
+«Заказывал мебель, изготовили качественно и в срок.
+Жена очень довольна, говорит удобно пользоваться.» (Нуржаиб Гебеков, 2026-08-28)
+«Очень отличная компания, отличная мебель.Всем довольна и обязательно вас всем буду советовать 👍🏻» (Милана Халикова, 2026-08-27)</t>
+        </is>
+      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>ежедневно 09:00-21:00</t>
+          <t>ежедневно 10:00-19:00</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>сайт был (novamebel05.ru), домен удалён</t>
         </is>
       </c>
     </row>
@@ -1772,28 +1868,28 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Воронеж</t>
+          <t>Уфа</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Reroom</t>
+          <t>Эксклюзив, студия мебели</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни, Мебель для ванных комнат, Корпусная мебель, Изделия из камня для помещений</t>
+          <t>Мебель на заказ, Мебельные фасады, Мебель для кухни, Корпусная мебель</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1803,32 +1899,37 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79202222306</t>
+          <t>https://t.me/+79279262727</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79202222306</t>
+          <t>https://wa.me/79279262727</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>+7‒920‒222‒23‒06</t>
+          <t>+7‒927‒926‒27‒27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>улица Лётчика Колесниченко, 65а</t>
+          <t>Айская улица, 64/2а</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/voronezh/firm/70000001067470840</t>
+          <t>https://2gis.ru/ufa/firm/70000001069284561</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>сайт был (exklusiv02.ru), домен удалён</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1838,59 +1939,64 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Тюмень</t>
+          <t>Томск</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Студия мебели 72</t>
+          <t>Бородихин.Мебель, мебельная фирма</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Детская мебель</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>соцсети (http://t.me/borodixinmebel)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79220751863</t>
+          <t>https://t.me/+79528901616</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>+7 (3452) 933‒424</t>
+          <t>+7‒952‒890‒16‒16</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Николая Чаплина улица, 115</t>
+          <t>улица Смирнова, 9 ст10</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/tyumen/firm/70000001033925374</t>
+          <t>https://2gis.ru/tomsk/firm/70000001063613662</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>сайт был (borodixin.ru), домен удалён</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1900,63 +2006,68 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Барнаул</t>
+          <t>Томск</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Престиж, мебельный салон</t>
+          <t>Стиль кухни, салон кухонной мебели</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные магазины, Мягкая мебель, Корпусная мебель</t>
+          <t>Мебель на заказ, Мебель для кухни, Изделия из камня для помещений</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>соцсети (http://max.ru/channel_Stmebel)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/prestizh22</t>
+          <t>https://t.me/stmebel70</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79646037139</t>
+          <t>https://wa.me/79138122002</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>+7‒964‒603‒71‒39</t>
+          <t>+7‒913‒812‒20‒02</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Павловский тракт, 251ж</t>
+          <t>улица Нахимова, 8 ст2</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/barnaul/firm/70000001025293075</t>
+          <t>https://2gis.ru/tomsk/firm/70000001037714736</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1966,63 +2077,68 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Томск</t>
+          <t>Барнаул</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Marle, студия мебели</t>
+          <t>Сибирь-интерьер, компания по производству мебели и дизайну интерьера</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
+          <t>Мебель на заказ, Мебельные магазины, Мебель для кухни, Изделия из камня для помещений, Мебель для общественного питания, Мебель для ванных комнат, Мебель для культурно-досуговых учреждений, Мебель для салонов красоты, Детская мебель, Корпусная мебель, Мебель для учебных учреждений, Перегородки, Стеновые панели, Торгово-выставочное оборудование</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>соцсети (http://t.me/marletmsk)</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79131111387</t>
+          <t>https://t.me/+79236498160</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79234577445</t>
+          <t>https://wa.me/79619968080</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>+7‒9‒234‒577‒445</t>
+          <t>+7‒923‒649‒81‒60</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>улица Пушкина, 59/1</t>
+          <t>улица Челюскинцев, 82</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/tomsk/firm/70000001063814452</t>
+          <t>https://2gis.ru/barnaul/firm/70000001064302618</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>сайт был (rubmebel.ru), домен удалён</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2032,63 +2148,68 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Владивосток</t>
+          <t>Воронеж</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ИнДом, торгово-производственная компания</t>
+          <t>Артмакс</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Офисная мебель, Распиловка древесины, Мебель для ванных комнат, Детская мебель</t>
+          <t>Мебель на заказ, Мебель для кухни</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>taplink (http://taplink.cc/indom)</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+aZJHfuP5ChQzNTRi</t>
+          <t>https://t.me/+79997220805</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79089939190</t>
+          <t>https://wa.me/79997220805</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>+7‒908‒993‒91‒90</t>
+          <t>+7‒999‒722‒08‒05</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Можайская улица, 28в</t>
+          <t>улица Куколкина, 33а</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/vladivostok/firm/3518965489996252</t>
+          <t>https://2gis.ru/voronezh/firm/70000001079579082</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2098,28 +2219,28 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Челябинск</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Текстура, семейная студия мебели и интерьерных решений</t>
+          <t>ПурПур, студия мебели на заказ</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Дизайн интерьеров, Офисная мебель, Мебель для кухни, Детская мебель, Мебель для ванных комнат, Торгово-выставочное оборудование</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Детская мебель, Распиловка древесины</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2129,32 +2250,37 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79923303208</t>
+          <t>https://t.me/+79995872500</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79292120201</t>
+          <t>https://wa.me/79995872500</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>+7‒992‒330‒32‒08</t>
+          <t>+7‒999‒587‒25‒00</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Мраморская улица, 6</t>
+          <t>Енисейская улица, 28</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/ekaterinburg/firm/70000001064278509</t>
+          <t>https://2gis.ru/chelyabinsk/firm/70000001087815397</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2169,54 +2295,59 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Нова, салон мебели</t>
+          <t>МастерМебель05, фабрика</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные магазины, Корпусная мебель, Детская мебель, Мягкая мебель</t>
+          <t>Мебель на заказ, Корпусная мебель, Жалюзи</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>соцсети (http://t.me/novamebel05)</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79884403011</t>
+          <t>https://wa.me/79604213277</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>+7‒988‒440‒30‒11</t>
+          <t>+7‒960‒421‒32‒77</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>проспект Гамидова, 81/2</t>
+          <t>2-й Мятный тупик, 11</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/makhachkala/firm/70000001021645284</t>
+          <t>https://2gis.ru/makhachkala/firm/70000001025450155</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2226,28 +2357,28 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Уфа</t>
+          <t>Ижевск</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Эксклюзив, студия мебели</t>
+          <t>Корпус Дизайн, шоурум</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные фасады, Мебель для кухни, Корпусная мебель</t>
+          <t>Мебель на заказ, Мебельные магазины, Корпусная мебель, Офисная мебель, Мебель для общественного питания, Мебель для салонов красоты, Мебель для учебных учреждений, Мебель для кухни, Мебель для ванных комнат</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2257,32 +2388,37 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79279262727</t>
+          <t>https://t.me/+79935332796</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79279262727</t>
+          <t>https://wa.me/79935332796</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>+7‒927‒926‒27‒27</t>
+          <t>+7‒993‒533‒27‒96</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Айская улица, 64/2а</t>
+          <t>улица Максима Горького, 151</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/ufa/firm/70000001069284561</t>
+          <t>https://2gis.ru/izhevsk/firm/70000001055115085</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2292,59 +2428,68 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Томск</t>
+          <t>Нижний Новгород</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Бородихин.Мебель, мебельная фирма</t>
+          <t>Loft Point, студия по изготовлению мебели</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Офисная мебель, Детская мебель, Мебель для ванных комнат</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>соцсети (http://t.me/borodixinmebel)</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79528901616</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr"/>
+          <t>https://t.me/+79043969500</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/79043969500</t>
+        </is>
+      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>+7‒952‒890‒16‒16</t>
+          <t>+7‒904‒396‒95‒00</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>улица Смирнова, 9 ст10</t>
+          <t>Трудовая улица, 7</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/tomsk/firm/70000001063613662</t>
+          <t>https://2gis.ru/n_novgorod/firm/70000001083491971</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2354,63 +2499,68 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Томск</t>
+          <t>Ярославль</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Стиль кухни, салон кухонной мебели</t>
+          <t>Бабич, шоурум</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни, Изделия из камня для помещений</t>
+          <t>Мебель на заказ, Мебель из стекла, Мебель для ванных комнат, Сборка мебели, Мебель для культурно-досуговых учреждений, Корпусная мебель, Мебель для кухни, Офисная мебель, Детская мебель, Мебельная фурнитура</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>соцсети (http://max.ru/channel_Stmebel)</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/stmebel70</t>
+          <t>https://t.me/+79201384292</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79138122002</t>
+          <t>https://wa.me/79201384292</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>+7‒913‒812‒20‒02</t>
+          <t>+7‒920‒138‒42‒92</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>улица Нахимова, 8 ст2</t>
+          <t>Ленинградский проспект, 33</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/tomsk/firm/70000001037714736</t>
+          <t>https://2gis.ru/yaroslavl/firm/70000001035304727</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>домен mebelbabich.ru пустой (заглушка reg.ru); есть визитка на orgs.biz</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2420,28 +2570,28 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Барнаул</t>
+          <t>Челябинск</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Сибирь-интерьер, компания по производству мебели и дизайну интерьера</t>
+          <t>Папа может, компания</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные магазины, Мебель для кухни, Изделия из камня для помещений, Мебель для общественного питания, Мебель для ванных комнат, Мебель для культурно-досуговых учреждений, Мебель для салонов красоты, Детская мебель, Корпусная мебель, Мебель для учебных учреждений, Перегородки, Стеновые панели, Торгово-выставочное оборудование</t>
+          <t>Мебель на заказ, Детская мебель, Мебель для кухни, Корпусная мебель</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2451,32 +2601,37 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79236498160</t>
+          <t>https://t.me/+79514573301</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79619968080</t>
+          <t>https://wa.me/79514573301</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>+7‒923‒649‒81‒60</t>
+          <t>+7‒951‒457‒33‒01</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>улица Челюскинцев, 82</t>
+          <t>улица Дзержинского, 93Б</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/barnaul/firm/70000001064302618</t>
+          <t>https://2gis.ru/chelyabinsk/firm/70000001021792530</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>есть только визитка на orgs.biz (бесплатный каталог)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2486,28 +2641,28 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Воронеж</t>
+          <t>Новосибирск</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Артмакс</t>
+          <t>Мдф-Технологии, производственная компания по изготовлению крашенных мебельных фасадов</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни</t>
+          <t>Мебель на заказ, Мебельные фабрики, Мебельные фасады, Ремонт мебели, Мебель для ванных комнат, Корпусная мебель, Мебель для кухни, ЛДСП, ДВПО, МДФ</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2517,32 +2672,37 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79997220805</t>
+          <t>https://t.me/+79607926858</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79997220805</t>
+          <t>https://wa.me/79607926858</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>+7‒999‒722‒08‒05</t>
+          <t>+7‒960‒792‒68‒58</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>улица Куколкина, 33а</t>
+          <t>улица Королёва, 40 к1</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/voronezh/firm/70000001079579082</t>
+          <t>https://2gis.ru/novosibirsk/firm/70000001041642077</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2552,28 +2712,28 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Челябинск</t>
+          <t>Саратов</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ПурПур, студия мебели на заказ</t>
+          <t>Трио, салон мебели</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Детская мебель, Распиловка древесины</t>
+          <t>Мебель на заказ, Мебельные магазины, Мебель для кухни, Корпусная мебель</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2583,32 +2743,37 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79995872500</t>
+          <t>https://t.me/trio_saratov</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79995872500</t>
+          <t>https://wa.me/79272266081</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>+7‒999‒587‒25‒00</t>
+          <t>+7 (8452) 46‒60‒81</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Енисейская улица, 28</t>
+          <t>Симбирская улица, 154</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/chelyabinsk/firm/70000001087815397</t>
+          <t>https://2gis.ru/saratov/firm/70000001019760997</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>домен трио.рф-вида пустой; салон продаёт «Кухни Трио», сайт у московской фабрики</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2618,28 +2783,28 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Махачкала</t>
+          <t>Уфа</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>МастерМебель05, фабрика</t>
+          <t>Основа Кухни</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Жалюзи</t>
+          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель, Дизайн интерьеров, Детская мебель, Бытовая техника</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2647,30 +2812,39 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/osnovaufa</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79604213277</t>
+          <t>https://wa.me/79867037001</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>+7‒960‒421‒32‒77</t>
+          <t>+7‒937‒500‒39‒99</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2-й Мятный тупик, 11</t>
+          <t>улица Менделеева, 141</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/makhachkala/firm/70000001025450155</t>
+          <t>https://2gis.ru/ufa/firm/70000001111173917</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2680,21 +2854,21 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Ижевск</t>
+          <t>Томск</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Корпус Дизайн, шоурум</t>
+          <t>Проект М, компания по производству корпусной мебели</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные магазины, Корпусная мебель, Офисная мебель, Мебель для общественного питания, Мебель для салонов красоты, Мебель для учебных учреждений, Мебель для кухни, Мебель для ванных комнат</t>
+          <t>Мебель на заказ, Мебельные фабрики, Офисная мебель, Мебель для кухни, Мебельные фасады, Корпусная мебель</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>5</v>
@@ -2711,32 +2885,37 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79935332796</t>
+          <t>https://t.me/+79138591361</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79935332796</t>
+          <t>https://wa.me/79138591361</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>+7‒993‒533‒27‒96</t>
+          <t>+7‒913‒859‒13‒61</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>улица Максима Горького, 151</t>
+          <t>улица Карла Маркса, 7</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/izhevsk/firm/70000001055115085</t>
+          <t>https://2gis.ru/tomsk/firm/70000001112648571</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2746,28 +2925,28 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Нижний Новгород</t>
+          <t>Томск</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Loft Point, студия по изготовлению мебели</t>
+          <t>Теремок, мебельная компания</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Офисная мебель, Детская мебель, Мебель для ванных комнат</t>
+          <t>Мебель на заказ, Погонажные изделия, Пило- и лесоматериалы, Корпусная мебель, Мебель для кухни, Офисная мебель</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2777,63 +2956,68 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79043969500</t>
+          <t>https://t.me/+79138202739</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79043969500</t>
+          <t>https://wa.me/79138202739</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>+7‒904‒396‒95‒00</t>
+          <t>+7‒913‒820‒33‒66</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Трудовая улица, 7</t>
+          <t>Мариинский переулок, 22/1</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/n_novgorod/firm/70000001083491971</t>
+          <t>https://2gis.ru/tomsk/firm/70000001054141987</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Ярославль</t>
+          <t>Ростов-на-Дону</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Бабич, шоурум</t>
+          <t>Мебелармо, мебельная фабрика</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель из стекла, Мебель для ванных комнат, Сборка мебели, Мебель для культурно-досуговых учреждений, Корпусная мебель, Мебель для кухни, Офисная мебель, Детская мебель, Мебельная фурнитура</t>
+          <t>Мебель на заказ, Корпусная мебель, Мягкая мебель, Мебель для кухни</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2843,63 +3027,68 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79201384292</t>
+          <t>https://t.me/+79613002860</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79201384292</t>
+          <t>https://wa.me/79613002860</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>+7‒920‒138‒42‒92</t>
+          <t>+7‒960‒455‒83‒33</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Ленинградский проспект, 33</t>
+          <t>улица Вавилова, 53</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/yaroslavl/firm/70000001035304727</t>
+          <t>https://2gis.ru/rostov/firm/70000001053120497</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Челябинск</t>
+          <t>Ростов-на-Дону</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Папа может, компания</t>
+          <t>Кухни Эксперт, салон кухонной мебели</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Детская мебель, Мебель для кухни, Корпусная мебель</t>
+          <t>Мебель на заказ, Мебельные магазины, Мебель для кухни</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>4.6</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2909,63 +3098,64 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79514573301</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>https://wa.me/79514573301</t>
-        </is>
-      </c>
+          <t>https://t.me/Kuhni_express1</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>+7‒951‒457‒33‒01</t>
+          <t>+7 (863) 298‒14‒88</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>улица Дзержинского, 93Б</t>
+          <t>улица Малиновского, 25</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/chelyabinsk/firm/70000001021792530</t>
+          <t>https://2gis.ru/rostov/firm/70000001032492711</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Новосибирск</t>
+          <t>Самара</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Мдф-Технологии, производственная компания по изготовлению крашенных мебельных фасадов</t>
+          <t>Мебель darom, студия мебели и фурнитуры</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные фабрики, Мебельные фасады, Ремонт мебели, Мебель для ванных комнат, Корпусная мебель, Мебель для кухни, ЛДСП, ДВПО, МДФ</t>
+          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель, Мебельная фурнитура, Офисная мебель</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2975,63 +3165,64 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79607926858</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>https://wa.me/79607926858</t>
-        </is>
-      </c>
+          <t>https://t.me/+79871562686</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>+7‒960‒792‒68‒58</t>
+          <t>+7‒987‒156‒26‒86</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>улица Королёва, 40 к1</t>
+          <t>Больничная улица, 39</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/novosibirsk/firm/70000001041642077</t>
+          <t>https://2gis.ru/samara/firm/70000001063906995</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Саратов</t>
+          <t>Омск</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Трио, салон мебели</t>
+          <t>Народные кухни, салон</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные магазины, Мебель для кухни, Корпусная мебель</t>
+          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3041,63 +3232,68 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/trio_saratov</t>
+          <t>https://t.me/+79045869551</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79272266081</t>
+          <t>https://wa.me/79509595241</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>+7 (8452) 46‒60‒81</t>
+          <t>+7‒950‒959‒52‒41</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Симбирская улица, 154</t>
+          <t>20 лет РККА, 179</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/saratov/firm/70000001019760997</t>
+          <t>https://2gis.ru/omsk/firm/70000001042900442</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Уфа</t>
+          <t>Самара</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Основа Кухни</t>
+          <t>Хвоя, студия мебели</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель, Дизайн интерьеров, Детская мебель, Бытовая техника</t>
+          <t>Мебель на заказ, Мебель из стекла, Корпусная мебель, Мягкая мебель, Офисная мебель</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3105,65 +3301,66 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/osnovaufa</t>
-        </is>
-      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79867037001</t>
+          <t>https://wa.me/79276972186</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>+7‒937‒500‒39‒99</t>
+          <t>+7‒937‒987‒06‒56</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>улица Менделеева, 141</t>
+          <t>Клиническая улица, 41/30</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/ufa/firm/70000001111173917</t>
+          <t>https://2gis.ru/samara/firm/70000001046774393</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Томск</t>
+          <t>Красноярск</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Проект М, компания по производству корпусной мебели</t>
+          <t>Акцент, мебельная компания</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные фабрики, Офисная мебель, Мебель для кухни, Мебельные фасады, Корпусная мебель</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Детская мебель</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3173,63 +3370,68 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79138591361</t>
+          <t>https://t.me/+79831434844</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79138591361</t>
+          <t>https://wa.me/79831434844</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>+7‒913‒859‒13‒61</t>
+          <t>+7‒983‒143‒48‒44</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>улица Карла Маркса, 7</t>
+          <t>улица Академика Вавилова, 3 ст8</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/tomsk/firm/70000001112648571</t>
+          <t>https://2gis.ru/krasnoyarsk/firm/70000001036394365</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Томск</t>
+          <t>Оренбург</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Теремок, мебельная компания</t>
+          <t>ПапоКарло, студия мебели</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Погонажные изделия, Пило- и лесоматериалы, Корпусная мебель, Мебель для кухни, Офисная мебель</t>
+          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3239,32 +3441,37 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79138202739</t>
+          <t>https://t.me/+79123451318</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79138202739</t>
+          <t>https://wa.me/79123451318</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>+7‒913‒820‒33‒66</t>
+          <t>+7‒912‒345‒13‒18</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Мариинский переулок, 22/1</t>
+          <t>улица Юркина, 9а к10</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/tomsk/firm/70000001054141987</t>
+          <t>https://2gis.ru/orenburg/firm/70000001064044144</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3274,63 +3481,68 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Ростов-на-Дону</t>
+          <t>Барнаул</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Мебелармо, мебельная фабрика</t>
+          <t>А|М, мастерская дизайнерской мебели</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мягкая мебель, Мебель для кухни</t>
+          <t>Мебель на заказ, Мебельные магазины, Корпусная мебель, Медицинская и лабораторная мебель, Мебельные фасады, Детская мебель, Мебель для кухни, Офисная мебель, Мебель для ванных комнат, Дизайн интерьеров, Мебель для культурно-досуговых учреждений, Мебель для общественного питания, Мебель для салонов красоты, Мебель для учебных учреждений, Сборка мебели, Стеновые панели</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>соцсети (http://t.me/comfort_barnaul22)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79613002860</t>
+          <t>https://t.me/+79029991137</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79613002860</t>
+          <t>https://wa.me/79029991137</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>+7‒960‒455‒83‒33</t>
+          <t>+7‒902‒999‒11‒37</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>улица Вавилова, 53</t>
+          <t>Бриллиантовая улица, 2/3</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/rostov/firm/70000001053120497</t>
+          <t>https://2gis.ru/barnaul/firm/70000001079618401</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3340,59 +3552,68 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Ростов-на-Дону</t>
+          <t>Владивосток</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Кухни Эксперт, салон кухонной мебели</t>
+          <t>Mebel25.vl, мебельная компания</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные магазины, Мебель для кухни</t>
+          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>соцсети (http://t.me/mebel25vl)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/Kuhni_express1</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr"/>
+          <t>https://t.me/mebel25vl</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/79841461494</t>
+        </is>
+      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>+7 (863) 298‒14‒88</t>
+          <t>+7‒984‒146‒14‒94</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>улица Малиновского, 25</t>
+          <t>Днепровская улица, 92 ст4</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/rostov/firm/70000001032492711</t>
+          <t>https://2gis.ru/vladivostok/firm/70000001021038480</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3402,28 +3623,28 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Самара</t>
+          <t>Махачкала</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Мебель darom, студия мебели и фурнитуры</t>
+          <t>Fiamma, салон мебели для кухни</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель, Мебельная фурнитура, Офисная мебель</t>
+          <t>Мебель на заказ, Мебельные магазины, Мебель для кухни</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3433,28 +3654,37 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79871562686</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr"/>
+          <t>https://t.me/+79289371236</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/79280639406</t>
+        </is>
+      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>+7‒987‒156‒26‒86</t>
+          <t>+7‒928‒063‒94‒06</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Больничная улица, 39</t>
+          <t>улица Азиза Алиева, 18</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/samara/firm/70000001063906995</t>
+          <t>https://2gis.ru/makhachkala/firm/70000001055884933</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3464,28 +3694,28 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Омск</t>
+          <t>Саратов</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Народные кухни, салон</t>
+          <t>Малина, мебельная студия</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Офисная мебель</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3495,32 +3725,37 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79045869551</t>
+          <t>https://t.me/+79658889900</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79509595241</t>
+          <t>https://wa.me/79658889900</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>+7‒950‒959‒52‒41</t>
+          <t>+7‒965‒888‒99‒00</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>20 лет РККА, 179</t>
+          <t>Астраханская улица, 88 к4</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/omsk/firm/70000001042900442</t>
+          <t>https://2gis.ru/saratov/firm/70000001062123931</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3530,28 +3765,28 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Самара</t>
+          <t>Хабаровск</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Хвоя, студия мебели</t>
+          <t>Атом, компания по производству мебели на заказ</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель из стекла, Корпусная мебель, Мягкая мебель, Офисная мебель</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Распиловка древесины</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3559,30 +3794,39 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/+79123890923</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79276972186</t>
+          <t>https://wa.me/79123890923</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>+7‒937‒987‒06‒56</t>
+          <t>+7‒912‒389‒09‒23</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Клиническая улица, 41/30</t>
+          <t>улица Калараша, 15</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/samara/firm/70000001046774393</t>
+          <t>https://2gis.ru/khabarovsk/firm/70000001099810582</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3592,28 +3836,28 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Красноярск</t>
+          <t>Владивосток</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Акцент, мебельная компания</t>
+          <t>Master hamster, компания</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Детская мебель</t>
+          <t>Мебель на заказ, Корпусная мебель, Распиловка древесины</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3623,32 +3867,37 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79831434844</t>
+          <t>https://t.me/+79084444190</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79831434844</t>
+          <t>https://wa.me/79084456036</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>+7‒983‒143‒48‒44</t>
+          <t>+7‒908‒444‒41‒90</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>улица Академика Вавилова, 3 ст8</t>
+          <t>Русская улица, 65</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/krasnoyarsk/firm/70000001036394365</t>
+          <t>https://2gis.ru/vladivostok/firm/70000001044504556</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3658,28 +3907,28 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Оренбург</t>
+          <t>Омск</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>ПапоКарло, студия мебели</t>
+          <t>Новые кухни, компания</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
+          <t>Мебель на заказ, Мебель для кухни</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3687,34 +3936,35 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/+79123451318</t>
-        </is>
-      </c>
+      <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79123451318</t>
+          <t>https://wa.me/79081174126</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>+7‒912‒345‒13‒18</t>
+          <t>+7‒908‒117‒41‒26</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>улица Юркина, 9а к10</t>
+          <t>улица Богдана Хмельницкого, 170</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/orenburg/firm/70000001064044144</t>
+          <t>https://2gis.ru/omsk/firm/70000001078910855</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3724,63 +3974,64 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Барнаул</t>
+          <t>Иркутск</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>А|М, мастерская дизайнерской мебели</t>
+          <t>Smeg, магазин бытовой техники</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные магазины, Корпусная мебель, Медицинская и лабораторная мебель, Мебельные фасады, Детская мебель, Мебель для кухни, Офисная мебель, Мебель для ванных комнат, Дизайн интерьеров, Мебель для культурно-досуговых учреждений, Мебель для общественного питания, Мебель для салонов красоты, Мебель для учебных учреждений, Сборка мебели, Стеновые панели</t>
+          <t>Мебель на заказ, Дизайн интерьеров, Бытовая техника, Сантехника, Мебель для кухни</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>соцсети (http://t.me/comfort_barnaul22)</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79029991137</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>https://wa.me/79029991137</t>
-        </is>
-      </c>
+          <t>https://t.me/smeg38</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>+7‒902‒999‒11‒37</t>
+          <t>+7 (3952) 20‒66‒54</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Бриллиантовая улица, 2/3</t>
+          <t>Байкальская улица, 89</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/barnaul/firm/70000001079618401</t>
+          <t>https://2gis.ru/irkutsk/firm/70000001099046452</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr"/>
       <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3790,63 +4041,60 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Владивосток</t>
+          <t>Оренбург</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Mebel25.vl, мебельная компания</t>
+          <t>Урал-мебель, мебельный цех</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для учебных учреждений, Детская мебель, Мебель для кухни</t>
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>соцсети (http://t.me/mebel25vl)</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/mebel25vl</t>
-        </is>
-      </c>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79841461494</t>
+          <t>https://wa.me/79877956197</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>+7‒984‒146‒14‒94</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>Днепровская улица, 92 ст4</t>
-        </is>
-      </c>
+          <t>+7‒987‒795‒61‒97</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/vladivostok/firm/70000001021038480</t>
+          <t>https://2gis.ru/orenburg/firm/6755927722203505</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3856,63 +4104,60 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Махачкала</t>
+          <t>Самара</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Fiamma, салон мебели для кухни</t>
+          <t>Фабрика кухни</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные магазины, Мебель для кухни</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>соцсети (http://t.me/kitchensamara)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79289371236</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>https://wa.me/79280639406</t>
-        </is>
-      </c>
+          <t>https://t.me/fabrika_kuhni163</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>+7‒928‒063‒94‒06</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>улица Азиза Алиева, 18</t>
-        </is>
-      </c>
+          <t>+7‒927‒291‒68‒67</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/makhachkala/firm/70000001055884933</t>
+          <t>https://2gis.ru/samara/firm/70000001070568232</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr"/>
       <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3922,63 +4167,68 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Саратов</t>
+          <t>Ижевск</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Малина, мебельная студия</t>
+          <t>Лавка, студия мебели</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Офисная мебель</t>
+          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель, Детская мебель, Мебель для ванных комнат, Офисная мебель</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>taplink (http://taplink.cc/lavkamebelizh)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79658889900</t>
+          <t>https://t.me/puchikoshka</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79658889900</t>
+          <t>https://wa.me/79829935129</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>+7‒965‒888‒99‒00</t>
+          <t>+7‒912‒445‒66‒54</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Астраханская улица, 88 к4</t>
+          <t>улица Орджоникидзе, 34</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/saratov/firm/70000001062123931</t>
+          <t>https://2gis.ru/izhevsk/firm/70000001075283790</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr"/>
       <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3988,28 +4238,28 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Хабаровск</t>
+          <t>Красноярск</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Атом, компания по производству мебели на заказ</t>
+          <t>докart, мебельная фирма</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Распиловка древесины</t>
+          <t>Мебель на заказ, Мебель для кухни</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4017,34 +4267,35 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/+79123890923</t>
-        </is>
-      </c>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79123890923</t>
+          <t>https://wa.me/79080101424</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>+7‒912‒389‒09‒23</t>
+          <t>+7‒908‒010‒14‒24</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>улица Калараша, 15</t>
+          <t>Базайская улица, 142</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/khabarovsk/firm/70000001099810582</t>
+          <t>https://2gis.ru/krasnoyarsk/firm/985690700234946</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr"/>
       <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4057,7 +4308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4076,6 +4327,7 @@
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="80" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4159,6 +4411,11 @@
           <t>часы работы</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>проверка сайта</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -4168,28 +4425,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Владивосток</t>
+          <t>Махачкала</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Master hamster, компания</t>
+          <t>Гранд, мебельная фирма</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Распиловка древесины</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -4197,34 +4454,35 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/+79084444190</t>
-        </is>
-      </c>
+      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79084456036</t>
+          <t>https://wa.me/79882222919</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>+7‒908‒444‒41‒90</t>
+          <t>+7‒988‒222‒29‒19</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Русская улица, 65</t>
+          <t>Ясная улица, 70</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/vladivostok/firm/70000001044504556</t>
+          <t>https://2gis.ru/makhachkala/firm/70000001117129887</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4234,59 +4492,64 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Омск</t>
+          <t>Уфа</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Новые кухни, компания</t>
+          <t>Акварель, фабрика кухни</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>https://wa.me/79081174126</t>
-        </is>
-      </c>
+          <t>соцсети (http://t.me/fabrikaakvarelufa http://max.ru/channel_akvarelufa)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/akvarelkuhni</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>+7‒908‒117‒41‒26</t>
+          <t>+7‒993‒136‒04‒04</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>улица Богдана Хмельницкого, 170</t>
+          <t>улица Героя Василия Утина, 2</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/omsk/firm/70000001078910855</t>
+          <t>https://2gis.ru/ufa/firm/70000001117781963</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4296,28 +4559,28 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Иркутск</t>
+          <t>Ижевск</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Smeg, магазин бытовой техники</t>
+          <t>Бюро104</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Дизайн интерьеров, Бытовая техника, Сантехника, Мебель для кухни</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Мебель для ванных комнат, Детская мебель, Офисная мебель</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -4327,59 +4590,385 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/smeg38</t>
+          <t>https://t.me/vstrkntv</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>+7 (3952) 20‒66‒54</t>
+          <t>+7‒982‒995‒46‒46</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Байкальская улица, 89</t>
+          <t>улица Холмогорова, 115</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/irkutsk/firm/70000001099046452</t>
+          <t>https://2gis.ru/izhevsk/firm/70000001112734041</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="80" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>приоритет</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>город</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>рубрика</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>отзывов</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>рейтинг</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>дата последнего отзыва</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>сайт (нет / соцсети / taplink)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>телефон</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>адрес</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ссылка на карточку 2ГИС</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>фото (ссылки)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>отзывы</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>часы работы</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>проверка сайта</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>GaStone, фабрика мебели</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель, Мебель для ванных комнат, Облицовочный камень</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/+79225601631</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Цвиллинга, 1</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>https://2gis.ru/ekaterinburg/firm/70000001100412421</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>есть сайт gastone.ru (бренд на сайте)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Саратов</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>1001Идея, мебельная компания</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Детская мебель, Офисная мебель</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>taplink (http://taplink.cc/1001idea)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/+79020428371</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/79020428371</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>+7 (8452) 60‒15‒15</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Геофизическая улица, 9</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>https://2gis.ru/saratov/firm/70000001054576304</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>есть сайт idea1001.ru (совпали телефон и почта)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Тюмень</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Paderin, мебельная мастерская</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель, Офисная мебель, Детская мебель, Мебель для ванных комнат</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/+79923112860</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>+7 (3452) 70‒21‒02</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>улица Фармана Салманова, 18</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>https://2gis.ru/tyumen/firm/70000001087652176</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>есть сайт bigmebel-tmn.ru (бренд Paderin на сайте)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Оренбург</t>
+          <t>Тюмень</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Урал-мебель, мебельный цех</t>
+          <t>Аватти, студия мебели</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для учебных учреждений, Детская мебель, Мебель для кухни</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Детская мебель, Мебель для ванных комнат, Изделия из камня для помещений, Офисная мебель</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>11</v>
+        <v>231</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -4387,181 +4976,204 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/+79582526486</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79877956197</t>
+          <t>https://wa.me/79582526486</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>+7‒987‒795‒61‒97</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>+7‒958‒252‒64‒86</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>улица Пожарных и спасателей, 3 к1</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/orenburg/firm/6755927722203505</t>
+          <t>https://2gis.ru/tyumen/firm/70000001064905837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>есть сайт awatti-mebel.ru (телефон совпал)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Самара</t>
+          <t>Тюмень</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Фабрика кухни</t>
+          <t>Шкаф, офис продаж</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни</t>
+          <t>Мебель на заказ, Мягкая мебель, Детская мебель, Мебель для кухни, Корпусная мебель, Офисная мебель, Мебельные фасады, Изделия из камня для помещений, Мебель для ванных комнат, Мебель для культурно-досуговых учреждений, Мебель для общественного питания, Медицинская и лабораторная мебель, Мебель для учебных учреждений, Металлическая мебель, Мебель из стекла, Мебель для салонов красоты, Распиловка древесины, ЛДСП, ДВПО, МДФ</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>соцсети (http://t.me/kitchensamara)</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/fabrika_kuhni163</t>
+          <t>https://t.me/+79088742331</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>+7‒927‒291‒68‒67</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>+7‒904‒498‒49‒44</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Полевая улица, 109 ст1</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/samara/firm/70000001070568232</t>
+          <t>https://2gis.ru/tyumen/firm/70000001055443836</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>есть сайт shkaf72.ru (совпал второй телефон из карточки)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Ижевск</t>
+          <t>Барнаул</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Лавка, студия мебели</t>
+          <t>Ависта, мебельная компания</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель, Детская мебель, Мебель для ванных комнат, Офисная мебель</t>
+          <t>Мебель на заказ, Мебельные фасады, Мебель для кухни, Корпусная мебель</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>taplink (http://taplink.cc/lavkamebelizh)</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/puchikoshka</t>
-        </is>
-      </c>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79829935129</t>
+          <t>https://wa.me/79132102115</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>+7‒912‒445‒66‒54</t>
+          <t>+7 (3852) 299‒922</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>улица Орджоникидзе, 34</t>
+          <t>проспект Космонавтов, 34ж</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/izhevsk/firm/70000001075283790</t>
+          <t>https://2gis.ru/barnaul/firm/563478234632390</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>есть сайт avistafasad.com (телефон совпал)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Красноярск</t>
+          <t>Владивосток</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>докart, мебельная фирма</t>
+          <t>Сити мебель, мебельная фабрика</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Перегородки, Изделия из камня для помещений</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>8</v>
+        <v>298</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -4569,216 +5181,39 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/+79020504333</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79080101424</t>
+          <t>https://wa.me/79241237111</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>+7‒908‒010‒14‒24</t>
+          <t>+7‒924‒123‒71‒11</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Базайская улица, 142</t>
+          <t>Выселковая улица, 39</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/krasnoyarsk/firm/985690700234946</t>
+          <t>https://2gis.ru/vladivostok/firm/70000001027532472</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Махачкала</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Гранд, мебельная фирма</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>https://wa.me/79882222919</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>+7‒988‒222‒29‒19</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>Ясная улица, 70</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>https://2gis.ru/makhachkala/firm/70000001117129887</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Уфа</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Акварель, фабрика кухни</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>соцсети (http://t.me/fabrikaakvarelufa http://max.ru/channel_akvarelufa)</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/akvarelkuhni</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>+7‒993‒136‒04‒04</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>улица Героя Василия Утина, 2</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>https://2gis.ru/ufa/firm/70000001117781963</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Ижевск</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Бюро104</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Мебель для ванных комнат, Детская мебель, Офисная мебель</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/vstrkntv</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>+7‒982‒995‒46‒46</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>улица Холмогорова, 115</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>https://2gis.ru/izhevsk/firm/70000001112734041</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>есть сайт city-mebel.com (телефон совпал)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/baza-rossiya.xlsx
+++ b/baza-rossiya.xlsx
@@ -625,61 +625,151 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>Владивосток</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Сити мебель, мебельная фабрика</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Перегородки, Изделия из камня для помещений</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/+79020504333</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/79241237111</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>+7‒924‒123‒71‒11</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Выселковая улица, 39</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>https://2gis.ru/vladivostok/firm/70000001027532472</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>https://i2.photo.2gis.com/images/branch/0/30258560057154802_2f85.jpg
+https://i6.photo.2gis.com/images/branch/0/30258560057154801_e62c.jpg
+https://i8.photo.2gis.com/images/branch/25/3518437227585068_e41f.jpg
+https://i0.photo.2gis.com/images/branch/0/30258560057154800_fbda.jpg
+https://i2.photo.2gis.com/photo-gallery/e6e137ad-6992-408e-bdde-dc607c63c3cb.jpg
+https://i8.photo.2gis.com/photo-gallery/e1364147-12f9-4254-a0d2-5d4f47b27b81.jpg</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>«Искали узкий шкаф-купе в коридор, чтобы не перекрывал проход. В Сити Мебель нашли подходящий вариант. Двери выбрали зеркальные во весь рост, коридор теперь визуально кажется шире и светлее. Профиль ходит бесшумно, шкаф то что надо!» (Дина ., 2026-10-12)
+«Ставлю пятерку нашей прихожей. Красиво получилось, очень гармонично сочетается с нашим кухонным гарнитуром, смотрится как с одного набора. Уже порекомендовал вас сестре как хорошую мебельную компанию😏» (Матвей vl, 2026-10-09)
+«Шкаф отличный! Цвет подошел под кровать один в один. Вместительный, полок внутри сделали много, как я и просила. Никаких сколов или царапин при доставке не обнаружила» (Кира Демина, 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>ежедневно 09:30-18:00</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>сайт был (city-mebel.com), домен удалён: проверено по DNS 17.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>Оренбург</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Мебель Концепт 56, мебельная компания</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Мебель на заказ, Мебель для кухни, Офисная мебель, Корпусная мебель</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E4" s="2" t="n">
         <v>138</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>taplink (http://taplink.cc/concept056)</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>https://t.me/+79033662614</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/79033662614</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>+7‒903‒366‒26‒14</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>проезд Автоматики, 12 лит В</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/orenburg/firm/70000001088992897</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>https://i9.photo.2gis.com/photo-gallery/cc4a8ca6-7267-43fc-afc4-21a6cffce369.jpg
 https://i6.photo.2gis.com/photo-gallery/d2d892f8-d037-4762-95bf-a35fadcd2301.jpg
@@ -689,83 +779,83 @@
 https://i7.photo.2gis.com/photo-gallery/16d2acff-67fa-4a61-a7cd-43a180a88590.jpg</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>«Мебель Концепт 56 приятно удивил уровнем сервиса. Менеджеры помогли с выбором, а готовая мебель оказалась просто отличной.» (ALEKSANDR ALESHIN, 2026-10-14)
 «Очень довольны сотрудничеством с компанией Мебель Концепт 56. Мебель качественная, стильная и полностью соответствует нашим ожиданиям.» (Татьяна Абрамова, 2026-10-09)
 «заказали тут кухню по совету друзей. Нам понравилось с вами сотрудничать изготовили в срок установили быстро. От кухни восторге» (Гриша Каримов, 2026-10-05)</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>ежедневно 10:00-19:00</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Челябинск</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Диамант, мебельный салон</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E5" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F5" s="2" t="n">
         <v>4.9</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>https://t.me/+79507404273</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>+7‒950‒740‒42‒73</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Каслинская улица, 23</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/chelyabinsk/firm/70000001081038759</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>https://i6.photo.2gis.com/photo-gallery/72c1d0ed-afcf-42ce-b380-b8c7226efb90.jpg
 https://i3.photo.2gis.com/photo-gallery/d4fd00ab-7e27-453d-b01b-203d361ba5df.jpg
@@ -775,87 +865,87 @@
 https://i8.photo.2gis.com/photo-gallery/1ac3778d-0643-4ee2-93ed-ea36842847fc.jpg</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>«Давно мечтала о кухне с островом, и Диамант воплотил мечту в реальность! Места теперь хватает всей нашей большой семье. Готовить одно удовольствие.» (Любовь Беликова, 2026-10-17)
 «Сборка прошла на удивление быстро и чисто. Мастера даже пропылесосили за собой. Приятно удивлен таким сервисом.» (Тимур Ласточкин, 2026-10-16)
 «Ксения - волшебница! Помогла выбрать такой сложный оттенок для фасадов, который идеально вписался в интерьер. Я в восторге))» (Анна Демидова, 2026-10-15)</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>ежедневно 10:00-21:00</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Красноярск</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Мастерская дизайна</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Мебель на заказ, Корпусная мебель, Мебель для кухни</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E6" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>4.9</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>https://t.me/+79131773957</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/79131773957</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>+7‒913‒177‒39‒57</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>улица Шахтёров, 65</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/krasnoyarsk/firm/70000001019390807</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>https://i8.photo.2gis.com/photo-gallery/8489f0e3-2f87-4a18-8d24-fb51a405fcec.jpg
 https://i8.photo.2gis.com/photo-gallery/9fccd053-349e-444c-9338-ac4e5de79bae.jpg
@@ -865,83 +955,83 @@
 https://i7.photo.2gis.com/photo-gallery/b11581d7-1f2e-44b3-b46b-1745d5624736.jpg</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>«Идеальный сервис от и до! Заказывали мебель и технику с установкой под ключ. Работа руководства и мастеров максимально слаженная, подход к клиенту отличный. Качеством сборки и отношением очень довольны. Рекомендую на все 100%» (Дмитрий P, 2026-07-08)
 «Делали у ребят кухню, книжный шкаф и тумбу под телевизор! Очень понравилось работать, все досконально замеряют, учитывают каждый нюанс, если вам важны детали, то точно обращайтесь к ним!» (Юлия Разумкина, 2026-05-06)
 «Обращаемся в мастерскую дизайна уже не в первый раз, качество на высоте. Все сотрудники мастера своего дела, ответственные, Екатерина воплощает все наши пожелания!!! Мы довольны вашей работой.» (Вера Монич, 2026-01-08)</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>ежедневно 10:00-19:00</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Тюмень</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Mebelm, студия мебели</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Мебель на заказ, Мебельные магазины, Корпусная мебель, Мебель для кухни, Детская мебель, Офисная мебель</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E7" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>соцсети (http://t.me/mebm72)</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>https://t.me/mebelm72</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>+7‒929‒269‒52‒94</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>улица Федюнинского, 43</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/tyumen/firm/70000001069445291</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>https://i0.photo.2gis.com/photo-gallery/a82d491a-04c4-4a94-a3bb-643de74fa396.jpg
 https://i8.photo.2gis.com/photo-gallery/37ab22c0-c946-4e68-9ce4-f2aa7daea0e8.jpg
@@ -951,83 +1041,83 @@
 https://i6.photo.2gis.com/photo-gallery/74dae07b-363a-4757-a502-1271e0de80ce.jpg</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>«Хочу выразить благодарность менеджеру Ладе, за отличную работу на этапе заказа. Мы только что оформили договор на покупку кухни, саму мебель еще ждем. Лада, учла все наши пожелания и предложила удобные варианты планировки.» (Оксана Самарцева, 2026-09-10)
 «Заказали в МебельМ кухню, удалось вписаться в бюджет! Ждём изготовления и установки.» (Игорь М, 2026-08-18)
 «Все было отлично очень советую менеджер Александра спасибо вам отлично проконсультировали мастер своего дела спасибо !» (Владимир Астахов, 2026-08-07)</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>ежедневно 10:00-21:00</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Иркутск</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Сандера, студия кухни и корпусной мебели</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E8" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>4.9</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>https://t.me/+79247057628</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>+7‒924‒600‒33‒03</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>улица Рабочего Штаба, 66</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/irkutsk/firm/70000001065493213</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>https://i2.photo.2gis.com/images/branch/0/30258560173175962_889c.jpg
 https://i1.photo.2gis.com/photo-gallery/15bfbad6-9208-4708-9a62-2e53b06c5bc1.jpg
@@ -1037,7 +1127,7 @@
 https://i0.photo.2gis.com/photo-gallery/4ca68973-6bce-4939-bca2-ff8a48793416.jpg</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>«Заказывали шкаф именно в данной компании по рекомендации коллег.
 Отличный сервис,все изготовили и установили точно в срок.Хорошо,что компания предоставляет от себя рассрочку,это удобно.
@@ -1047,76 +1137,76 @@
 Про гарнитур подруги сказали, что это мечта любой хозяйки))» (Мария Стрыгина, 2026-05-20)</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>пн выходной, вт-сб 11:00-19:00, вс выходной</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Красноярск</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Мебелиссимо</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Мебель на заказ, Корпусная мебель, Детская мебель, Мебель для ванных комнат, Мебель для кухни</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/79130397007</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>+7‒913‒039‒70‒07</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>улица Академика Вавилова, 1 ст9</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/krasnoyarsk/firm/70000001056207594</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>https://i1.photo.2gis.com/photo-gallery/a5971d5d-bc29-4e3f-b1a0-1229eda79bd8.jpg
 https://i4.photo.2gis.com/images/branch/0/30258560065176713_1714.jpg
@@ -1126,7 +1216,7 @@
 https://i2.photo.2gis.com/photo-gallery/1f65b1b9-172b-4334-abac-a3eb49357a3a.jpg</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>«Делала ремонт родителям, заказывала всю мебель тут. Оптимальное соотношение цена/качество. Ответственная компания, сроки выдержаны, хорошие монтажники, все мелкие нюансы доведены до конечного результата 👌
 Советую!» (Анна Данильченко, 2026-05-28)
@@ -1134,76 +1224,76 @@
 «Сделали раньше срока, на всех этапах помогали и консультировали, подсказывали, изготовили и установили идеально, все зазоры ровные ( в плоть) до миллиметра, огромное спасибо Денису и мастеру Александру за шикарную кухню!» (Семён Клявзер, 2026-03-23)</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>пн-пт 10:00-19:00, сб 10:00-15:00, вс выходной</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>под вопросом: ник ВК совпадает с kukhni-krasnoyarsk.ru, но телефон на сайте другой, похоже на чужой сайт-агрегатор</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Иркутск</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Кухни-Тейге, компания по производству кухонь и шкафов</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Мебель на заказ, Офисная мебель, Мебель для ванных комнат, Детская мебель, Корпусная мебель, Мебель для кухни</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E10" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F10" s="2" t="n">
         <v>4.7</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>https://t.me/+79148810902</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>+7‒908‒774‒46‒22</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Байкальская улица, 126/3</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/irkutsk/firm/70000001056539637</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>https://i8.photo.2gis.com/photo-gallery/9448c8f9-1d09-4a01-86fd-194d330887a0.jpg
 https://i1.photo.2gis.com/photo-gallery/79bb0b2f-c1c9-47f6-8d68-14af37af7bb1.jpg
@@ -1213,87 +1303,87 @@
 https://i2.photo.2gis.com/photo-gallery/3232cd3f-be5d-4128-97b8-a86c46449eca.jpg</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>«Заказывали год назад кухню. Илья сразу предупредил, что ожидание примерно 3-4 месяца. Но это того стоило. Теперь это наше любимое место в доме. Кухня просторная и многофункциональная. Спасибо большое.» (Евгения Дейнеко, 2026-09-10)
 «Не место красит человека а человек место, предельно честный диалог, а это в наше время далеко не последнее качество. Соотношение цены и качество - безупречно. Рекомендую !!!» (Светлана Шурыгина, 2026-06-02)
 «Подход к тем, которые только планируют кухонный гарнитур. Предлагая варианты и нужные решения» (Александр Сорокин, 2025-07-19)</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>ежедневно 09:00-21:00</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Воронеж</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Reroom</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Мебель на заказ, Мебель для кухни, Мебель для ванных комнат, Корпусная мебель, Изделия из камня для помещений</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E11" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F11" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>https://t.me/+79202222306</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/79202222306</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>+7‒920‒222‒23‒06</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>улица Лётчика Колесниченко, 65а</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/voronezh/firm/70000001067470840</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>https://i7.photo.2gis.com/images/branch/0/30258560168471449_6e6a.jpg
 https://i6.photo.2gis.com/images/branch/0/30258560168471439_5047.jpg
@@ -1303,83 +1393,83 @@
 https://i3.photo.2gis.com/images/branch/0/30258560168471444_12e1.jpg</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>«Работой компании Reroom осталась довольна, кухонный гарнитур изготовили по необходимым размерам, доставили и установили качественно и в срок. Учли все пожелания!» (Евгения Тарасова, 2026-10-13)
 «Отличное соотношение цены и качества, доступные цены, кухня выглядит стильно и современно.» (Альбина Воронина, 2026-10-06)
 «Давно выбирала кухню. Пересмотрела кучу вариантов и выбор остановился на компании Reroom.Всё делают быстро, качественно, всем довольна» (Ксю Ник, 2026-10-04)</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>ежедневно 10:00-19:00</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Тюмень</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Студия мебели 72</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Детская мебель</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E12" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F12" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>https://t.me/+79220751863</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>+7 (3452) 933‒424</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Николая Чаплина улица, 115</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/tyumen/firm/70000001033925374</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>https://i3.photo.2gis.com/images/branch/0/30258560082794661_483f.jpg
 https://i4.photo.2gis.com/images/branch/13/1829587396678755_f370.jpg
@@ -1389,7 +1479,7 @@
 https://i8.photo.2gis.com/photo-gallery/f2268bf2-5e39-40e2-990b-5db65d4d5a99.jpg</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>«Лучшая студия для заказа мебели . Уже 4 года на постоянной основе желаем заказ.
 Менеджер Екатерина, мастеры Константин и Вадим все профессионалы с большой буквы . Качество и сервис на высоте ! Спасибо ❤️» (Тали Долгополова, 2026-07-24)
@@ -1398,80 +1488,80 @@
 И за качество мебели и за выполнению работу. Выполнили все своевременно. Обращаюсь не в первый раз» (Гавва Хусейнова, 2025-03-01)</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>пн-пт 10:00-18:00, сб-вс 11:00-17:00</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Барнаул</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Престиж, мебельный салон</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Мебель на заказ, Мебельные магазины, Мягкая мебель, Корпусная мебель</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E13" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F13" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>https://t.me/prestizh22</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/79646037139</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>+7‒964‒603‒71‒39</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>Павловский тракт, 251ж</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001025293075</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>https://i1.photo.2gis.com/photo-gallery/f67ec993-3083-44a5-9811-0f45cbc8468f.jpg
 https://i1.photo.2gis.com/images/branch/0/30258560085749641_2bb2.jpg
@@ -1481,87 +1571,87 @@
 https://i2.photo.2gis.com/images/branch/0/30258560081105444_7f4a.jpg</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>«Приобрёл кровать, матрац и диван, работа консультанта отличная, цены адекватные, модели изделий в красивом дизайне, ни как у большинства фабрик! Жду поставку мебели, надеюсь придет в отличном качестве!» (Алим Абдуллаев, 2026-07-24)
 «Купил шкаф-купе, очень доволен качеством. Отдельная благодарность мастерам Алексею и Сергею, которые учли все пожелания и собрали шкаф очень хорошо и качественно.» (Никита Колодченко, 2025-07-17)
 «Сегодня нам привезли и поставили прихожую,все оперативно быстро, мусор за собой убрали,все аккуратно, спасибо парням. Срок изготовления 20 дней.» (Светлана Нечаева, 2025-05-13)</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>ежедневно 10:00-21:00</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Томск</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Marle, студия мебели</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E14" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F14" s="2" t="n">
         <v>4.9</v>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>соцсети (http://t.me/marletmsk)</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>https://t.me/+79131111387</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/79234577445</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>+7‒9‒234‒577‒445</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>улица Пушкина, 59/1</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/tomsk/firm/70000001063814452</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>https://i1.photo.2gis.com/photo-gallery/88bf2580-4089-49ff-a170-39d7993e5d93.jpg
 https://i4.photo.2gis.com/photo-gallery/14a4d18a-b053-443e-a3bd-92857a358250.jpg
@@ -1571,87 +1661,87 @@
 https://i5.photo.2gis.com/photo-gallery/0bbeb0c7-c848-4819-9ae0-20ed6059306a.jpg</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>«Узнали о компании по рекомендации. Обращалась по изготовлению детской в дом . Сразу поняли друг друга и подобрали идеальный цвет и размер. Вежливый персонал. Также порадовала бесплатная доставка и установка. Однозначно рекомендую» (Рамазан, 2026-10-02)
 «С этой компанией уже больше 5 лет. Ставили себе и старшей дочери. Сейчас установили кухню и шкаф в новую квартиру. Все как всегда шикарно, а главное со вкусом» (Татьяна Краюхина, 2026-09-28)
 «В этой компании делали заказ новой кухни маме в подарок на юбилей. Привезли и собрали мебель в срок. Качество достойное, внешне кухня смотрится отлично» (Дарья Коровина, 2026-09-24)</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>ежедневно 10:00-21:00</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Владивосток</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>ИнДом, торгово-производственная компания</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Офисная мебель, Распиловка древесины, Мебель для ванных комнат, Детская мебель</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E15" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F15" s="2" t="n">
         <v>4.9</v>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>taplink (http://taplink.cc/indom)</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>https://t.me/+aZJHfuP5ChQzNTRi</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/79089939190</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>+7‒908‒993‒91‒90</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Можайская улица, 28в</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/vladivostok/firm/3518965489996252</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>https://i4.photo.2gis.com/images/branch/0/30258560079429485_dbcb.jpg
 https://i1.photo.2gis.com/images/branch/0/30258560077847459_d1f6.jpg
@@ -1661,7 +1751,7 @@
 https://i3.photo.2gis.com/images/branch/0/30258560093474605_3a46.jpg</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>«Все понравилось. Сделали в срок. Полная консультация по всем материалам.
 Спасибо.» (Денис Мельников, 2026-10-01)
@@ -1669,80 +1759,80 @@
 «Спасибо ребятам, все сделал очень хорошо. Цена вполне удовлетворительная, а качество на высоте! Возможно ещё закажем какую-то мебель» (Городской житель, 2025-12-19)</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>ежедневно 10:00-17:00</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Екатеринбург</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Текстура, семейная студия мебели и интерьерных решений</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Мебель на заказ, Корпусная мебель, Дизайн интерьеров, Офисная мебель, Мебель для кухни, Детская мебель, Мебель для ванных комнат, Торгово-выставочное оборудование</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E16" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F16" s="2" t="n">
         <v>4.9</v>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>https://t.me/+79923303208</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/79292120201</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>+7‒992‒330‒32‒08</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Мраморская улица, 6</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>https://2gis.ru/ekaterinburg/firm/70000001064278509</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>https://i2.photo.2gis.com/images/branch/0/30258560131054986_d293.jpg
 https://i3.photo.2gis.com/images/branch/0/30258560131013185_0e7a.jpg
@@ -1752,7 +1842,7 @@
 https://i3.photo.2gis.com/images/branch/0/30258560131054984_8e68.jpg</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>«Уже почти год любуюсь самой красивой кухней💜
 Спасибо Станиславу за то, что каждый шкафчик в квартире собирал с душой.
@@ -1762,101 +1852,14 @@
 «Не первый раз заказываем мебель у Ксении и Станислава. Два года назад установили отличную кухню. Теперь дошла очередь до шкафа в спальню. Результатом довольны! Отдельно замечу - не смотря на проблемы со стенами, Стас установил все идеально, до миллиметра 👍👍👍» (Alexander Pribylov, 2025-04-27)</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>ежедневно 11:00-20:00</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Махачкала</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Нова, салон мебели</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Мебель на заказ, Мебельные магазины, Корпусная мебель, Детская мебель, Мягкая мебель</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>соцсети (http://t.me/novamebel05)</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>https://wa.me/79884403011</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>+7‒988‒440‒30‒11</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>проспект Гамидова, 81/2</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>https://2gis.ru/makhachkala/firm/70000001021645284</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>https://i7.photo.2gis.com/photo-gallery/9321abb7-29e9-48a5-8668-7c10200875b9.jpg
-https://i4.photo.2gis.com/photo-gallery/cbf6e432-9022-4dcc-ad34-55f0214f77ae.jpg
-https://i7.photo.2gis.com/photo-gallery/c2102357-6933-4f6a-9b9f-e12cdbefee7f.jpg
-https://i0.photo.2gis.com/photo-gallery/35361992-e47c-4971-a03f-0f469bfa6eae.jpg
-https://i0.photo.2gis.com/photo-gallery/20cbc26d-efeb-46c3-a567-c7a6f8c94eca.jpg
-https://i1.photo.2gis.com/photo-gallery/0ef2eb4d-89ae-4ca5-acfa-a7bdd91c1454.jpg</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>«Все шикарно! Очень довольна ! Советую!!!» (Саида Цахаева, 2026-09-12)
-«Заказывал мебель, изготовили качественно и в срок.
-Жена очень довольна, говорит удобно пользоваться.» (Нуржаиб Гебеков, 2026-08-28)
-«Очень отличная компания, отличная мебель.Всем довольна и обязательно вас всем буду советовать 👍🏻» (Милана Халикова, 2026-08-27)</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>ежедневно 10:00-19:00</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>сайт был (novamebel05.ru), домен удалён</t>
         </is>
       </c>
     </row>
@@ -1868,58 +1871,54 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Уфа</t>
+          <t>Махачкала</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Эксклюзив, студия мебели</t>
+          <t>Нова, салон мебели</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные фасады, Мебель для кухни, Корпусная мебель</t>
+          <t>Мебель на заказ, Мебельные магазины, Корпусная мебель, Детская мебель, Мягкая мебель</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/+79279262727</t>
-        </is>
-      </c>
+          <t>соцсети (http://t.me/novamebel05)</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79279262727</t>
+          <t>https://wa.me/79884403011</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>+7‒927‒926‒27‒27</t>
+          <t>+7‒988‒440‒30‒11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Айская улица, 64/2а</t>
+          <t>проспект Гамидова, 81/2</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/ufa/firm/70000001069284561</t>
+          <t>https://2gis.ru/makhachkala/firm/70000001021645284</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr"/>
@@ -1927,7 +1926,7 @@
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>сайт был (exklusiv02.ru), домен удалён</t>
+          <t>сайт был (novamebel05.ru), домен удалён</t>
         </is>
       </c>
     </row>
@@ -1939,54 +1938,58 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Томск</t>
+          <t>Уфа</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Бородихин.Мебель, мебельная фирма</t>
+          <t>Эксклюзив, студия мебели</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни</t>
+          <t>Мебель на заказ, Мебельные фасады, Мебель для кухни, Корпусная мебель</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
         <v>34</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>соцсети (http://t.me/borodixinmebel)</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79528901616</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr"/>
+          <t>https://t.me/+79279262727</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/79279262727</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>+7‒952‒890‒16‒16</t>
+          <t>+7‒927‒926‒27‒27</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>улица Смирнова, 9 ст10</t>
+          <t>Айская улица, 64/2а</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/tomsk/firm/70000001063613662</t>
+          <t>https://2gis.ru/ufa/firm/70000001069284561</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
@@ -1994,7 +1997,7 @@
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>сайт был (borodixin.ru), домен удалён</t>
+          <t>сайт был (exklusiv02.ru), домен удалён</t>
         </is>
       </c>
     </row>
@@ -2011,53 +2014,49 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Стиль кухни, салон кухонной мебели</t>
+          <t>Бородихин.Мебель, мебельная фирма</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни, Изделия из камня для помещений</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>соцсети (http://max.ru/channel_Stmebel)</t>
+          <t>соцсети (http://t.me/borodixinmebel)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/stmebel70</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>https://wa.me/79138122002</t>
-        </is>
-      </c>
+          <t>https://t.me/+79528901616</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>+7‒913‒812‒20‒02</t>
+          <t>+7‒952‒890‒16‒16</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>улица Нахимова, 8 ст2</t>
+          <t>улица Смирнова, 9 ст10</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/tomsk/firm/70000001037714736</t>
+          <t>https://2gis.ru/tomsk/firm/70000001063613662</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr"/>
@@ -2065,7 +2064,7 @@
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+          <t>сайт был (borodixin.ru), домен удалён</t>
         </is>
       </c>
     </row>
@@ -2077,58 +2076,58 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Барнаул</t>
+          <t>Томск</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Сибирь-интерьер, компания по производству мебели и дизайну интерьера</t>
+          <t>Стиль кухни, салон кухонной мебели</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные магазины, Мебель для кухни, Изделия из камня для помещений, Мебель для общественного питания, Мебель для ванных комнат, Мебель для культурно-досуговых учреждений, Мебель для салонов красоты, Детская мебель, Корпусная мебель, Мебель для учебных учреждений, Перегородки, Стеновые панели, Торгово-выставочное оборудование</t>
+          <t>Мебель на заказ, Мебель для кухни, Изделия из камня для помещений</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>соцсети (http://max.ru/channel_Stmebel)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79236498160</t>
+          <t>https://t.me/stmebel70</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79619968080</t>
+          <t>https://wa.me/79138122002</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>+7‒923‒649‒81‒60</t>
+          <t>+7‒913‒812‒20‒02</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>улица Челюскинцев, 82</t>
+          <t>улица Нахимова, 8 ст2</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/barnaul/firm/70000001064302618</t>
+          <t>https://2gis.ru/tomsk/firm/70000001037714736</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
@@ -2136,7 +2135,7 @@
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>сайт был (rubmebel.ru), домен удалён</t>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
         </is>
       </c>
     </row>
@@ -2148,28 +2147,28 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Воронеж</t>
+          <t>Барнаул</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Артмакс</t>
+          <t>Сибирь-интерьер, компания по производству мебели и дизайну интерьера</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни</t>
+          <t>Мебель на заказ, Мебельные магазины, Мебель для кухни, Изделия из камня для помещений, Мебель для общественного питания, Мебель для ванных комнат, Мебель для культурно-досуговых учреждений, Мебель для салонов красоты, Детская мебель, Корпусная мебель, Мебель для учебных учреждений, Перегородки, Стеновые панели, Торгово-выставочное оборудование</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2179,27 +2178,27 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79997220805</t>
+          <t>https://t.me/+79236498160</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79997220805</t>
+          <t>https://wa.me/79619968080</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>+7‒999‒722‒08‒05</t>
+          <t>+7‒923‒649‒81‒60</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>улица Куколкина, 33а</t>
+          <t>улица Челюскинцев, 82</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/voronezh/firm/70000001079579082</t>
+          <t>https://2gis.ru/barnaul/firm/70000001064302618</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr"/>
@@ -2207,7 +2206,7 @@
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+          <t>сайт был (rubmebel.ru), домен удалён</t>
         </is>
       </c>
     </row>
@@ -2219,28 +2218,28 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Челябинск</t>
+          <t>Воронеж</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>ПурПур, студия мебели на заказ</t>
+          <t>Артмакс</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Детская мебель, Распиловка древесины</t>
+          <t>Мебель на заказ, Мебель для кухни</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2250,27 +2249,27 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79995872500</t>
+          <t>https://t.me/+79997220805</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79995872500</t>
+          <t>https://wa.me/79997220805</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>+7‒999‒587‒25‒00</t>
+          <t>+7‒999‒722‒08‒05</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Енисейская улица, 28</t>
+          <t>улица Куколкина, 33а</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/chelyabinsk/firm/70000001087815397</t>
+          <t>https://2gis.ru/voronezh/firm/70000001079579082</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
@@ -2290,28 +2289,28 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Махачкала</t>
+          <t>Челябинск</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>МастерМебель05, фабрика</t>
+          <t>ПурПур, студия мебели на заказ</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Жалюзи</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Детская мебель, Распиловка древесины</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2319,25 +2318,29 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/+79995872500</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79604213277</t>
+          <t>https://wa.me/79995872500</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>+7‒960‒421‒32‒77</t>
+          <t>+7‒999‒587‒25‒00</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2-й Мятный тупик, 11</t>
+          <t>Енисейская улица, 28</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/makhachkala/firm/70000001025450155</t>
+          <t>https://2gis.ru/chelyabinsk/firm/70000001087815397</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr"/>
@@ -2357,24 +2360,24 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Ижевск</t>
+          <t>Махачкала</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Корпус Дизайн, шоурум</t>
+          <t>МастерМебель05, фабрика</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные магазины, Корпусная мебель, Офисная мебель, Мебель для общественного питания, Мебель для салонов красоты, Мебель для учебных учреждений, Мебель для кухни, Мебель для ванных комнат</t>
+          <t>Мебель на заказ, Корпусная мебель, Жалюзи</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -2386,29 +2389,25 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/+79935332796</t>
-        </is>
-      </c>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79935332796</t>
+          <t>https://wa.me/79604213277</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>+7‒993‒533‒27‒96</t>
+          <t>+7‒960‒421‒32‒77</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>улица Максима Горького, 151</t>
+          <t>2-й Мятный тупик, 11</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/izhevsk/firm/70000001055115085</t>
+          <t>https://2gis.ru/makhachkala/firm/70000001025450155</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr"/>
@@ -2428,28 +2427,28 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Нижний Новгород</t>
+          <t>Ижевск</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Loft Point, студия по изготовлению мебели</t>
+          <t>Корпус Дизайн, шоурум</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Офисная мебель, Детская мебель, Мебель для ванных комнат</t>
+          <t>Мебель на заказ, Мебельные магазины, Корпусная мебель, Офисная мебель, Мебель для общественного питания, Мебель для салонов красоты, Мебель для учебных учреждений, Мебель для кухни, Мебель для ванных комнат</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2459,27 +2458,27 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79043969500</t>
+          <t>https://t.me/+79935332796</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79043969500</t>
+          <t>https://wa.me/79935332796</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>+7‒904‒396‒95‒00</t>
+          <t>+7‒993‒533‒27‒96</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Трудовая улица, 7</t>
+          <t>улица Максима Горького, 151</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/n_novgorod/firm/70000001083491971</t>
+          <t>https://2gis.ru/izhevsk/firm/70000001055115085</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr"/>
@@ -2499,28 +2498,28 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Ярославль</t>
+          <t>Нижний Новгород</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Бабич, шоурум</t>
+          <t>Loft Point, студия по изготовлению мебели</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель из стекла, Мебель для ванных комнат, Сборка мебели, Мебель для культурно-досуговых учреждений, Корпусная мебель, Мебель для кухни, Офисная мебель, Детская мебель, Мебельная фурнитура</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Офисная мебель, Детская мебель, Мебель для ванных комнат</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
         <v>21</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2530,27 +2529,27 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79201384292</t>
+          <t>https://t.me/+79043969500</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79201384292</t>
+          <t>https://wa.me/79043969500</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>+7‒920‒138‒42‒92</t>
+          <t>+7‒904‒396‒95‒00</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Ленинградский проспект, 33</t>
+          <t>Трудовая улица, 7</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/yaroslavl/firm/70000001035304727</t>
+          <t>https://2gis.ru/n_novgorod/firm/70000001083491971</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr"/>
@@ -2558,7 +2557,7 @@
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>домен mebelbabich.ru пустой (заглушка reg.ru); есть визитка на orgs.biz</t>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
         </is>
       </c>
     </row>
@@ -2570,28 +2569,28 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Челябинск</t>
+          <t>Ярославль</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Папа может, компания</t>
+          <t>Бабич, шоурум</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Детская мебель, Мебель для кухни, Корпусная мебель</t>
+          <t>Мебель на заказ, Мебель из стекла, Мебель для ванных комнат, Сборка мебели, Мебель для культурно-досуговых учреждений, Корпусная мебель, Мебель для кухни, Офисная мебель, Детская мебель, Мебельная фурнитура</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2601,27 +2600,27 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79514573301</t>
+          <t>https://t.me/+79201384292</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79514573301</t>
+          <t>https://wa.me/79201384292</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>+7‒951‒457‒33‒01</t>
+          <t>+7‒920‒138‒42‒92</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>улица Дзержинского, 93Б</t>
+          <t>Ленинградский проспект, 33</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/chelyabinsk/firm/70000001021792530</t>
+          <t>https://2gis.ru/yaroslavl/firm/70000001035304727</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr"/>
@@ -2629,7 +2628,7 @@
       <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>есть только визитка на orgs.biz (бесплатный каталог)</t>
+          <t>домен mebelbabich.ru пустой (заглушка reg.ru); есть визитка на orgs.biz</t>
         </is>
       </c>
     </row>
@@ -2641,28 +2640,28 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Новосибирск</t>
+          <t>Челябинск</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Мдф-Технологии, производственная компания по изготовлению крашенных мебельных фасадов</t>
+          <t>Папа может, компания</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные фабрики, Мебельные фасады, Ремонт мебели, Мебель для ванных комнат, Корпусная мебель, Мебель для кухни, ЛДСП, ДВПО, МДФ</t>
+          <t>Мебель на заказ, Детская мебель, Мебель для кухни, Корпусная мебель</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2672,27 +2671,27 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79607926858</t>
+          <t>https://t.me/+79514573301</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79607926858</t>
+          <t>https://wa.me/79514573301</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>+7‒960‒792‒68‒58</t>
+          <t>+7‒951‒457‒33‒01</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>улица Королёва, 40 к1</t>
+          <t>улица Дзержинского, 93Б</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/novosibirsk/firm/70000001041642077</t>
+          <t>https://2gis.ru/chelyabinsk/firm/70000001021792530</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
@@ -2700,7 +2699,7 @@
       <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+          <t>есть только визитка на orgs.biz (бесплатный каталог)</t>
         </is>
       </c>
     </row>
@@ -2712,17 +2711,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Саратов</t>
+          <t>Новосибирск</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Трио, салон мебели</t>
+          <t>Мдф-Технологии, производственная компания по изготовлению крашенных мебельных фасадов</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные магазины, Мебель для кухни, Корпусная мебель</t>
+          <t>Мебель на заказ, Мебельные фабрики, Мебельные фасады, Ремонт мебели, Мебель для ванных комнат, Корпусная мебель, Мебель для кухни, ЛДСП, ДВПО, МДФ</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
@@ -2733,7 +2732,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2743,27 +2742,27 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/trio_saratov</t>
+          <t>https://t.me/+79607926858</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79272266081</t>
+          <t>https://wa.me/79607926858</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>+7 (8452) 46‒60‒81</t>
+          <t>+7‒960‒792‒68‒58</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Симбирская улица, 154</t>
+          <t>улица Королёва, 40 к1</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/saratov/firm/70000001019760997</t>
+          <t>https://2gis.ru/novosibirsk/firm/70000001041642077</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr"/>
@@ -2771,7 +2770,7 @@
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>домен трио.рф-вида пустой; салон продаёт «Кухни Трио», сайт у московской фабрики</t>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
         </is>
       </c>
     </row>
@@ -2783,28 +2782,28 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Уфа</t>
+          <t>Саратов</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Основа Кухни</t>
+          <t>Трио, салон мебели</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель, Дизайн интерьеров, Детская мебель, Бытовая техника</t>
+          <t>Мебель на заказ, Мебельные магазины, Мебель для кухни, Корпусная мебель</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2814,27 +2813,27 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/osnovaufa</t>
+          <t>https://t.me/trio_saratov</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79867037001</t>
+          <t>https://wa.me/79272266081</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>+7‒937‒500‒39‒99</t>
+          <t>+7 (8452) 46‒60‒81</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>улица Менделеева, 141</t>
+          <t>Симбирская улица, 154</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/ufa/firm/70000001111173917</t>
+          <t>https://2gis.ru/saratov/firm/70000001019760997</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
@@ -2842,7 +2841,7 @@
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
+          <t>домен трио.рф-вида пустой; салон продаёт «Кухни Трио», сайт у московской фабрики</t>
         </is>
       </c>
     </row>
@@ -2854,17 +2853,17 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Томск</t>
+          <t>Уфа</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Проект М, компания по производству корпусной мебели</t>
+          <t>Основа Кухни</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные фабрики, Офисная мебель, Мебель для кухни, Мебельные фасады, Корпусная мебель</t>
+          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель, Дизайн интерьеров, Детская мебель, Бытовая техника</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
@@ -2875,7 +2874,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2885,27 +2884,27 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79138591361</t>
+          <t>https://t.me/osnovaufa</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79138591361</t>
+          <t>https://wa.me/79867037001</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>+7‒913‒859‒13‒61</t>
+          <t>+7‒937‒500‒39‒99</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>улица Карла Маркса, 7</t>
+          <t>улица Менделеева, 141</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/tomsk/firm/70000001112648571</t>
+          <t>https://2gis.ru/ufa/firm/70000001111173917</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr"/>
@@ -2930,23 +2929,23 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Теремок, мебельная компания</t>
+          <t>Проект М, компания по производству корпусной мебели</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Погонажные изделия, Пило- и лесоматериалы, Корпусная мебель, Мебель для кухни, Офисная мебель</t>
+          <t>Мебель на заказ, Мебельные фабрики, Офисная мебель, Мебель для кухни, Мебельные фасады, Корпусная мебель</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2956,27 +2955,27 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79138202739</t>
+          <t>https://t.me/+79138591361</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79138202739</t>
+          <t>https://wa.me/79138591361</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>+7‒913‒820‒33‒66</t>
+          <t>+7‒913‒859‒13‒61</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Мариинский переулок, 22/1</t>
+          <t>улица Карла Маркса, 7</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/tomsk/firm/70000001054141987</t>
+          <t>https://2gis.ru/tomsk/firm/70000001112648571</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr"/>
@@ -2991,33 +2990,33 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Ростов-на-Дону</t>
+          <t>Томск</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Мебелармо, мебельная фабрика</t>
+          <t>Теремок, мебельная компания</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мягкая мебель, Мебель для кухни</t>
+          <t>Мебель на заказ, Погонажные изделия, Пило- и лесоматериалы, Корпусная мебель, Мебель для кухни, Офисная мебель</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3027,27 +3026,27 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79613002860</t>
+          <t>https://t.me/+79138202739</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79613002860</t>
+          <t>https://wa.me/79138202739</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>+7‒960‒455‒83‒33</t>
+          <t>+7‒913‒820‒33‒66</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>улица Вавилова, 53</t>
+          <t>Мариинский переулок, 22/1</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/rostov/firm/70000001053120497</t>
+          <t>https://2gis.ru/tomsk/firm/70000001054141987</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr"/>
@@ -3055,7 +3054,7 @@
       <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>не проверялось</t>
+          <t>сайт не найден (карточка, почта, подбор домена, веб-поиск)</t>
         </is>
       </c>
     </row>
@@ -3072,23 +3071,23 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Кухни Эксперт, салон кухонной мебели</t>
+          <t>Мебелармо, мебельная фабрика</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные магазины, Мебель для кухни</t>
+          <t>Мебель на заказ, Корпусная мебель, Мягкая мебель, Мебель для кухни</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3098,23 +3097,27 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/Kuhni_express1</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr"/>
+          <t>https://t.me/+79613002860</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/79613002860</t>
+        </is>
+      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>+7 (863) 298‒14‒88</t>
+          <t>+7‒960‒455‒83‒33</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>улица Малиновского, 25</t>
+          <t>улица Вавилова, 53</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/rostov/firm/70000001032492711</t>
+          <t>https://2gis.ru/rostov/firm/70000001053120497</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr"/>
@@ -3134,28 +3137,28 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Самара</t>
+          <t>Ростов-на-Дону</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Мебель darom, студия мебели и фурнитуры</t>
+          <t>Кухни Эксперт, салон кухонной мебели</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель, Мебельная фурнитура, Офисная мебель</t>
+          <t>Мебель на заказ, Мебельные магазины, Мебель для кухни</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3165,23 +3168,23 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79871562686</t>
+          <t>https://t.me/Kuhni_express1</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>+7‒987‒156‒26‒86</t>
+          <t>+7 (863) 298‒14‒88</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Больничная улица, 39</t>
+          <t>улица Малиновского, 25</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/samara/firm/70000001063906995</t>
+          <t>https://2gis.ru/rostov/firm/70000001032492711</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr"/>
@@ -3201,28 +3204,28 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Омск</t>
+          <t>Самара</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Народные кухни, салон</t>
+          <t>Мебель darom, студия мебели и фурнитуры</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
+          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель, Мебельная фурнитура, Офисная мебель</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3232,27 +3235,23 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79045869551</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>https://wa.me/79509595241</t>
-        </is>
-      </c>
+          <t>https://t.me/+79871562686</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>+7‒950‒959‒52‒41</t>
+          <t>+7‒987‒156‒26‒86</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>20 лет РККА, 179</t>
+          <t>Больничная улица, 39</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/omsk/firm/70000001042900442</t>
+          <t>https://2gis.ru/samara/firm/70000001063906995</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr"/>
@@ -3272,28 +3271,28 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Самара</t>
+          <t>Омск</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Хвоя, студия мебели</t>
+          <t>Народные кухни, салон</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель из стекла, Корпусная мебель, Мягкая мебель, Офисная мебель</t>
+          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3301,25 +3300,29 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/+79045869551</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79276972186</t>
+          <t>https://wa.me/79509595241</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>+7‒937‒987‒06‒56</t>
+          <t>+7‒950‒959‒52‒41</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Клиническая улица, 41/30</t>
+          <t>20 лет РККА, 179</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/samara/firm/70000001046774393</t>
+          <t>https://2gis.ru/omsk/firm/70000001042900442</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr"/>
@@ -3339,28 +3342,28 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Красноярск</t>
+          <t>Самара</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Акцент, мебельная компания</t>
+          <t>Хвоя, студия мебели</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Детская мебель</t>
+          <t>Мебель на заказ, Мебель из стекла, Корпусная мебель, Мягкая мебель, Офисная мебель</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3368,29 +3371,25 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/+79831434844</t>
-        </is>
-      </c>
+      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79831434844</t>
+          <t>https://wa.me/79276972186</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>+7‒983‒143‒48‒44</t>
+          <t>+7‒937‒987‒06‒56</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>улица Академика Вавилова, 3 ст8</t>
+          <t>Клиническая улица, 41/30</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/krasnoyarsk/firm/70000001036394365</t>
+          <t>https://2gis.ru/samara/firm/70000001046774393</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr"/>
@@ -3410,28 +3409,28 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Оренбург</t>
+          <t>Красноярск</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>ПапоКарло, студия мебели</t>
+          <t>Акцент, мебельная компания</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Детская мебель</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3441,27 +3440,27 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79123451318</t>
+          <t>https://t.me/+79831434844</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79123451318</t>
+          <t>https://wa.me/79831434844</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>+7‒912‒345‒13‒18</t>
+          <t>+7‒983‒143‒48‒44</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>улица Юркина, 9а к10</t>
+          <t>улица Академика Вавилова, 3 ст8</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/orenburg/firm/70000001064044144</t>
+          <t>https://2gis.ru/krasnoyarsk/firm/70000001036394365</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr"/>
@@ -3481,58 +3480,58 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Барнаул</t>
+          <t>Оренбург</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>А|М, мастерская дизайнерской мебели</t>
+          <t>ПапоКарло, студия мебели</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные магазины, Корпусная мебель, Медицинская и лабораторная мебель, Мебельные фасады, Детская мебель, Мебель для кухни, Офисная мебель, Мебель для ванных комнат, Дизайн интерьеров, Мебель для культурно-досуговых учреждений, Мебель для общественного питания, Мебель для салонов красоты, Мебель для учебных учреждений, Сборка мебели, Стеновые панели</t>
+          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>соцсети (http://t.me/comfort_barnaul22)</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79029991137</t>
+          <t>https://t.me/+79123451318</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79029991137</t>
+          <t>https://wa.me/79123451318</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>+7‒902‒999‒11‒37</t>
+          <t>+7‒912‒345‒13‒18</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Бриллиантовая улица, 2/3</t>
+          <t>улица Юркина, 9а к10</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/barnaul/firm/70000001079618401</t>
+          <t>https://2gis.ru/orenburg/firm/70000001064044144</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr"/>
@@ -3552,58 +3551,58 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Владивосток</t>
+          <t>Барнаул</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Mebel25.vl, мебельная компания</t>
+          <t>А|М, мастерская дизайнерской мебели</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
+          <t>Мебель на заказ, Мебельные магазины, Корпусная мебель, Медицинская и лабораторная мебель, Мебельные фасады, Детская мебель, Мебель для кухни, Офисная мебель, Мебель для ванных комнат, Дизайн интерьеров, Мебель для культурно-досуговых учреждений, Мебель для общественного питания, Мебель для салонов красоты, Мебель для учебных учреждений, Сборка мебели, Стеновые панели</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>соцсети (http://t.me/mebel25vl)</t>
+          <t>соцсети (http://t.me/comfort_barnaul22)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/mebel25vl</t>
+          <t>https://t.me/+79029991137</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79841461494</t>
+          <t>https://wa.me/79029991137</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>+7‒984‒146‒14‒94</t>
+          <t>+7‒902‒999‒11‒37</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Днепровская улица, 92 ст4</t>
+          <t>Бриллиантовая улица, 2/3</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/vladivostok/firm/70000001021038480</t>
+          <t>https://2gis.ru/barnaul/firm/70000001079618401</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr"/>
@@ -3623,58 +3622,58 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Махачкала</t>
+          <t>Владивосток</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Fiamma, салон мебели для кухни</t>
+          <t>Mebel25.vl, мебельная компания</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебельные магазины, Мебель для кухни</t>
+          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>соцсети (http://t.me/mebel25vl)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79289371236</t>
+          <t>https://t.me/mebel25vl</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79280639406</t>
+          <t>https://wa.me/79841461494</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>+7‒928‒063‒94‒06</t>
+          <t>+7‒984‒146‒14‒94</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>улица Азиза Алиева, 18</t>
+          <t>Днепровская улица, 92 ст4</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/makhachkala/firm/70000001055884933</t>
+          <t>https://2gis.ru/vladivostok/firm/70000001021038480</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr"/>
@@ -3694,28 +3693,28 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Саратов</t>
+          <t>Махачкала</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Малина, мебельная студия</t>
+          <t>Fiamma, салон мебели для кухни</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Офисная мебель</t>
+          <t>Мебель на заказ, Мебельные магазины, Мебель для кухни</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3725,27 +3724,27 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79658889900</t>
+          <t>https://t.me/+79289371236</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79658889900</t>
+          <t>https://wa.me/79280639406</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>+7‒965‒888‒99‒00</t>
+          <t>+7‒928‒063‒94‒06</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Астраханская улица, 88 к4</t>
+          <t>улица Азиза Алиева, 18</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/saratov/firm/70000001062123931</t>
+          <t>https://2gis.ru/makhachkala/firm/70000001055884933</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr"/>
@@ -3765,28 +3764,28 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Хабаровск</t>
+          <t>Саратов</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Атом, компания по производству мебели на заказ</t>
+          <t>Малина, мебельная студия</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Распиловка древесины</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Офисная мебель</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
         <v>14</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3796,27 +3795,27 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79123890923</t>
+          <t>https://t.me/+79658889900</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79123890923</t>
+          <t>https://wa.me/79658889900</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>+7‒912‒389‒09‒23</t>
+          <t>+7‒965‒888‒99‒00</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>улица Калараша, 15</t>
+          <t>Астраханская улица, 88 к4</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/khabarovsk/firm/70000001099810582</t>
+          <t>https://2gis.ru/saratov/firm/70000001062123931</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr"/>
@@ -3836,28 +3835,28 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Владивосток</t>
+          <t>Хабаровск</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Master hamster, компания</t>
+          <t>Атом, компания по производству мебели на заказ</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Распиловка древесины</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Распиловка древесины</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3867,27 +3866,27 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/+79084444190</t>
+          <t>https://t.me/+79123890923</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79084456036</t>
+          <t>https://wa.me/79123890923</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>+7‒908‒444‒41‒90</t>
+          <t>+7‒912‒389‒09‒23</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Русская улица, 65</t>
+          <t>улица Калараша, 15</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/vladivostok/firm/70000001044504556</t>
+          <t>https://2gis.ru/khabarovsk/firm/70000001099810582</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr"/>
@@ -3907,28 +3906,28 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Омск</t>
+          <t>Владивосток</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Новые кухни, компания</t>
+          <t>Master hamster, компания</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни</t>
+          <t>Мебель на заказ, Корпусная мебель, Распиловка древесины</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3936,25 +3935,29 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/+79084444190</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79081174126</t>
+          <t>https://wa.me/79084456036</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>+7‒908‒117‒41‒26</t>
+          <t>+7‒908‒444‒41‒90</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>улица Богдана Хмельницкого, 170</t>
+          <t>Русская улица, 65</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/omsk/firm/70000001078910855</t>
+          <t>https://2gis.ru/vladivostok/firm/70000001044504556</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr"/>
@@ -3974,28 +3977,28 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Иркутск</t>
+          <t>Омск</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Smeg, магазин бытовой техники</t>
+          <t>Новые кухни, компания</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Дизайн интерьеров, Бытовая техника, Сантехника, Мебель для кухни</t>
+          <t>Мебель на заказ, Мебель для кухни</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
         <v>11</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -4003,25 +4006,25 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/smeg38</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/79081174126</t>
+        </is>
+      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>+7 (3952) 20‒66‒54</t>
+          <t>+7‒908‒117‒41‒26</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Байкальская улица, 89</t>
+          <t>улица Богдана Хмельницкого, 170</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/irkutsk/firm/70000001099046452</t>
+          <t>https://2gis.ru/omsk/firm/70000001078910855</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr"/>
@@ -4041,17 +4044,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Оренбург</t>
+          <t>Иркутск</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Урал-мебель, мебельный цех</t>
+          <t>Smeg, магазин бытовой техники</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для учебных учреждений, Детская мебель, Мебель для кухни</t>
+          <t>Мебель на заказ, Дизайн интерьеров, Бытовая техника, Сантехника, Мебель для кухни</t>
         </is>
       </c>
       <c r="E48" s="2" t="n">
@@ -4062,7 +4065,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4070,21 +4073,25 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>https://wa.me/79877956197</t>
-        </is>
-      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/smeg38</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>+7‒987‒795‒61‒97</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr"/>
+          <t>+7 (3952) 20‒66‒54</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Байкальская улица, 89</t>
+        </is>
+      </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/orenburg/firm/6755927722203505</t>
+          <t>https://2gis.ru/irkutsk/firm/70000001099046452</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr"/>
@@ -4104,50 +4111,50 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Самара</t>
+          <t>Оренбург</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Фабрика кухни</t>
+          <t>Урал-мебель, мебельный цех</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для учебных учреждений, Детская мебель, Мебель для кухни</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>соцсети (http://t.me/kitchensamara)</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/fabrika_kuhni163</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr"/>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/79877956197</t>
+        </is>
+      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>+7‒927‒291‒68‒67</t>
+          <t>+7‒987‒795‒61‒97</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/samara/firm/70000001070568232</t>
+          <t>https://2gis.ru/orenburg/firm/6755927722203505</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr"/>
@@ -4167,58 +4174,50 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Ижевск</t>
+          <t>Самара</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Лавка, студия мебели</t>
+          <t>Фабрика кухни</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель, Детская мебель, Мебель для ванных комнат, Офисная мебель</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>taplink (http://taplink.cc/lavkamebelizh)</t>
+          <t>соцсети (http://t.me/kitchensamara)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/puchikoshka</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>https://wa.me/79829935129</t>
-        </is>
-      </c>
+          <t>https://t.me/fabrika_kuhni163</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>+7‒912‒445‒66‒54</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>улица Орджоникидзе, 34</t>
-        </is>
-      </c>
+          <t>+7‒927‒291‒68‒67</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/izhevsk/firm/70000001075283790</t>
+          <t>https://2gis.ru/samara/firm/70000001070568232</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr"/>
@@ -4238,54 +4237,58 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Красноярск</t>
+          <t>Ижевск</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>докart, мебельная фирма</t>
+          <t>Лавка, студия мебели</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Мебель для кухни</t>
+          <t>Мебель на заказ, Мебель для кухни, Корпусная мебель, Детская мебель, Мебель для ванных комнат, Офисная мебель</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
+          <t>taplink (http://taplink.cc/lavkamebelizh)</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/puchikoshka</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79080101424</t>
+          <t>https://wa.me/79829935129</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>+7‒908‒010‒14‒24</t>
+          <t>+7‒912‒445‒66‒54</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Базайская улица, 142</t>
+          <t>улица Орджоникидзе, 34</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/krasnoyarsk/firm/985690700234946</t>
+          <t>https://2gis.ru/izhevsk/firm/70000001075283790</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr"/>
@@ -4308,7 +4311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4425,17 +4428,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Махачкала</t>
+          <t>Красноярск</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Гранд, мебельная фирма</t>
+          <t>докart, мебельная фирма</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни</t>
+          <t>Мебель на заказ, Мебель для кухни</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -4446,7 +4449,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -4457,22 +4460,22 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/79882222919</t>
+          <t>https://wa.me/79080101424</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>+7‒988‒222‒29‒19</t>
+          <t>+7‒908‒010‒14‒24</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Ясная улица, 70</t>
+          <t>Базайская улица, 142</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/makhachkala/firm/70000001117129887</t>
+          <t>https://2gis.ru/krasnoyarsk/firm/985690700234946</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
@@ -4492,12 +4495,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Уфа</t>
+          <t>Махачкала</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Акварель, фабрика кухни</t>
+          <t>Гранд, мебельная фирма</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -4506,40 +4509,40 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>соцсети (http://t.me/fabrikaakvarelufa http://max.ru/channel_akvarelufa)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/akvarelkuhni</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/79882222919</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>+7‒993‒136‒04‒04</t>
+          <t>+7‒988‒222‒29‒19</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>улица Героя Василия Утина, 2</t>
+          <t>Ясная улица, 70</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/ufa/firm/70000001117781963</t>
+          <t>https://2gis.ru/makhachkala/firm/70000001117129887</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr"/>
@@ -4559,17 +4562,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Ижевск</t>
+          <t>Уфа</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Бюро104</t>
+          <t>Акварель, фабрика кухни</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Мебель для ванных комнат, Детская мебель, Офисная мебель</t>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -4580,39 +4583,106 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>соцсети (http://t.me/fabrikaakvarelufa http://max.ru/channel_akvarelufa)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/vstrkntv</t>
+          <t>https://t.me/akvarelkuhni</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>+7‒982‒995‒46‒46</t>
+          <t>+7‒993‒136‒04‒04</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>улица Холмогорова, 115</t>
+          <t>улица Героя Василия Утина, 2</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>https://2gis.ru/izhevsk/firm/70000001112734041</t>
+          <t>https://2gis.ru/ufa/firm/70000001117781963</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>не проверялось</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Ижевск</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Бюро104</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Мебель для ванных комнат, Детская мебель, Офисная мебель</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/vstrkntv</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>+7‒982‒995‒46‒46</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>улица Холмогорова, 115</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>https://2gis.ru/izhevsk/firm/70000001112734041</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>не проверялось</t>
         </is>
@@ -4629,7 +4699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5144,77 +5214,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Владивосток</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Сити мебель, мебельная фабрика</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Мебель на заказ, Корпусная мебель, Мебель для кухни, Перегородки, Изделия из камня для помещений</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>298</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>https://t.me/+79020504333</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>https://wa.me/79241237111</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>+7‒924‒123‒71‒11</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>Выселковая улица, 39</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>https://2gis.ru/vladivostok/firm/70000001027532472</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>есть сайт city-mebel.com (телефон совпал)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
